--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,409 +656,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4457000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3850000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3878000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3661000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3884000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3595000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3786000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3661000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4100000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3887000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3910000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3982000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4453000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3978000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3870000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4357000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3991000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4093000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4177000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4149000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4559000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4529000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4701000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1960000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1936000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1959000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2015000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1784000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1885000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1958000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1859000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1975000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1989000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1987000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2063000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2372000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2128000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2091000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2279000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2033000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="U9" s="3">
-        <v>2258000</v>
       </c>
       <c r="V9" s="3">
         <v>2258000</v>
       </c>
       <c r="W9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="X9" s="3">
         <v>2693000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2552000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2668000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2497000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1914000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1919000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1646000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2100000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1710000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1828000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1802000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2125000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1898000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1923000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1919000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2081000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1850000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1779000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2078000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1958000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1864000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1919000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1891000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1866000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1977000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2033000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1091,100 +1103,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E12" s="3">
         <v>253000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>240000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>234000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>210000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>175000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>228000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>225000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>249000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>222000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>243000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>254000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>296000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>238000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>242000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>221000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>232000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>487000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>276000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>261000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>295000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>311000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>290000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>317000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>346000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>531000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>469000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>432000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>684000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1275,100 +1291,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>470000</v>
+        <v>652000</v>
       </c>
       <c r="E14" s="3">
-        <v>1448000</v>
+        <v>465000</v>
       </c>
       <c r="F14" s="3">
+        <v>1449000</v>
+      </c>
+      <c r="G14" s="3">
         <v>561000</v>
       </c>
-      <c r="G14" s="3">
-        <v>1854000</v>
-      </c>
       <c r="H14" s="3">
+        <v>1978000</v>
+      </c>
+      <c r="I14" s="3">
         <v>321000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1683000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1502000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>893000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>183000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>247000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>360000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>374000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5077000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>516000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>764000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>561000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>832000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1323000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>561000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3804000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1165000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>855000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>520000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>205000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1384,44 +1406,44 @@
       <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="3">
         <v>20000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>27000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>31000</v>
       </c>
       <c r="P15" s="3">
         <v>31000</v>
       </c>
       <c r="Q15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="R15" s="3">
         <v>30000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>35000</v>
       </c>
       <c r="U15" s="3">
         <v>35000</v>
@@ -1430,28 +1452,28 @@
         <v>35000</v>
       </c>
       <c r="W15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="X15" s="3">
         <v>24000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>51000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>41000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>46000</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>11</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>11</v>
@@ -1459,8 +1481,11 @@
       <c r="AF15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1490,192 +1515,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3735000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3495000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4524000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3659000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4739000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4837000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3176000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4735000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4374000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4022000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3264000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3328000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3548000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4048000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8320000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3697000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4166000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3843000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4174000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4821000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4015000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7709000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4513000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4715000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E18" s="3">
         <v>355000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-646000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-855000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-953000</v>
+      </c>
+      <c r="I18" s="3">
         <v>419000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-949000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-713000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>78000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>623000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>582000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>434000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>405000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>173000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>191000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>148000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-81000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-644000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>134000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>378000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>895000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1708,230 +1740,237 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-33000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-52000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-23000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-73000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-51000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-27000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>124000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>17000</v>
       </c>
       <c r="R20" s="3">
         <v>17000</v>
       </c>
       <c r="S20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="T20" s="3">
         <v>22000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>11000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>14000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>30000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>290000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1045000</v>
+      </c>
+      <c r="E21" s="3">
         <v>605000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-398000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>306000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-558000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-656000</v>
+      </c>
+      <c r="I21" s="3">
         <v>717000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-577000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-410000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>325000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>943000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>853000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>759000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>773000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>572000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>607000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>586000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>340000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-174000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>586000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>501000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>460000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>865000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E22" s="3">
         <v>247000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>216000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>260000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>237000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>230000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>225000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>238000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>180000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>232000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>240000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>239000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>241000</v>
       </c>
       <c r="P22" s="3">
         <v>241000</v>
@@ -1943,233 +1982,242 @@
         <v>241000</v>
       </c>
       <c r="S22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="T22" s="3">
         <v>209000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>219000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>226000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>227000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>231000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>240000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>231000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>218000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>221000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>219000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>526000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E23" s="3">
         <v>75000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-914000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-258000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1101000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-1199000</v>
+      </c>
+      <c r="I23" s="3">
         <v>166000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-971000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-175000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>382000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>308000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>144000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>137000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-51000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-39000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-292000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-850000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-84000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-213000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-250000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>119000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>688000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-12000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-19000</v>
       </c>
-      <c r="G24" s="3">
-        <v>154000</v>
-      </c>
       <c r="H24" s="3">
+        <v>149000</v>
+      </c>
+      <c r="I24" s="3">
         <v>107000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-900000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-24000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>76000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>98000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>62000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-21000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-104000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-59000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-119000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-179000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-236000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>54000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>57000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2260,192 +2308,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>432000</v>
+      </c>
+      <c r="E26" s="3">
         <v>87000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-898000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-239000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1255000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-1348000</v>
+      </c>
+      <c r="I26" s="3">
         <v>59000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-260000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-973000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-151000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>306000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>210000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>82000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>158000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>53000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>80000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-303000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-671000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-93000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-187000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>613000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>634000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E27" s="3">
         <v>80000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-863000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-205000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1221000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-1314000</v>
+      </c>
+      <c r="I27" s="3">
         <v>56000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-232000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-955000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-159000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>292000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>207000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>77000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>150000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>140000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>69000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>109000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-314000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-689000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-105000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-283000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-241000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>530000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>580000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2536,8 +2593,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2580,8 +2640,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>11</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>11</v>
@@ -2598,11 +2658,11 @@
       <c r="V29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>11</v>
@@ -2610,11 +2670,11 @@
       <c r="Z29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>11</v>
@@ -2628,8 +2688,11 @@
       <c r="AF29" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2720,8 +2783,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2812,192 +2878,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E32" s="3">
         <v>33000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>52000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>23000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>73000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>51000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>27000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-17000</v>
       </c>
       <c r="R32" s="3">
         <v>-17000</v>
       </c>
       <c r="S32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="T32" s="3">
         <v>-22000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>40000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>56000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>777000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E33" s="3">
         <v>80000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-863000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-205000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1221000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-1314000</v>
+      </c>
+      <c r="I33" s="3">
         <v>56000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-232000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-955000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-159000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>292000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>207000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>77000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>150000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>140000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>69000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>109000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-314000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-689000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-105000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-283000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-241000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>530000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>580000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3088,197 +3163,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E35" s="3">
         <v>80000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-863000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-205000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1221000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-1314000</v>
+      </c>
+      <c r="I35" s="3">
         <v>56000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-232000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-955000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-159000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>292000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>207000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>77000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>150000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>140000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>69000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>109000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-314000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-689000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-105000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-283000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-241000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>530000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>580000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3311,8 +3395,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3345,100 +3430,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3226000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2249000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2669000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2143000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2801000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2225000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2058000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2175000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2165000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2045000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2436000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1743000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2177000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1827000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2402000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1804000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1975000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1241000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2165000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1973000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1782000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1875000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1861000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>963000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>680000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>599000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>900000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>988000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3529,376 +3618,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3408000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3385000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3539000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3435000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3696000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3730000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4471000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4253000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4529000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4046000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4488000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4572000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4581000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4385000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4545000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5189000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5676000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5254000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5260000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5108000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5822000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5665000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6061000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4022000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4051000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4109000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4118000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3833000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3859000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4049000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4012000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3818000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4167000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4362000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4406000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4403000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4516000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4361000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4290000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4422000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4636000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4850000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4782000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4731000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4866000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4971000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1830000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1740000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1771000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1805000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1721000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1639000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1586000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2011000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2061000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1896000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1536000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1680000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1844000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1432000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1473000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1601000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1391000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1411000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1530000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1568000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1459000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1475000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1818000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12486000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11425000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12088000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11501000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12051000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11453000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12164000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12451000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12573000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12154000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12822000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12401000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13005000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12160000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12781000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12884000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13464000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12542000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13805000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13431000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13794000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13881000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14711000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3989,192 +4093,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6147000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6028000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6130000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6171000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6158000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5990000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6181000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6396000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6477000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6547000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6658000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6641000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6855000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6709000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6611000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6710000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6950000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7111000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7232000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7302000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6868000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7101000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7213000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22564000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22410000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22856000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23763000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23903000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24826000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25537000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27102000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27506000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28011000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28541000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28747000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>29547000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>29536000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>34556000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34746000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>36078000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36535000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>37348000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>38013000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>38922000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>42930000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>43860000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4265,8 +4378,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4357,100 +4473,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2283000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2225000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2021000</v>
       </c>
       <c r="F52" s="3">
         <v>2021000</v>
       </c>
       <c r="G52" s="3">
-        <v>1894000</v>
+        <v>2021000</v>
       </c>
       <c r="H52" s="3">
+        <v>1899000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1983000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1110000</v>
       </c>
       <c r="K52" s="3">
         <v>1110000</v>
       </c>
       <c r="L52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="M52" s="3">
         <v>1139000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1174000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1215000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1233000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1332000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1043000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>990000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>978000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1058000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1039000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1108000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1099000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1149000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1246000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4541,100 +4663,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43480000</v>
+      </c>
+      <c r="E54" s="3">
         <v>42088000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43095000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43456000</v>
       </c>
-      <c r="G54" s="3">
-        <v>44006000</v>
-      </c>
       <c r="H54" s="3">
+        <v>44011000</v>
+      </c>
+      <c r="I54" s="3">
         <v>44252000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45932000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47059000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47666000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47851000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49195000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>49004000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>50640000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49737000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54991000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55330000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57470000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57246000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59424000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59854000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60683000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>65061000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>67030000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4667,8 +4795,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4701,560 +4830,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2602000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2280000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2508000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2381000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1887000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1635000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1901000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1750000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1686000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1514000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1551000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1692000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1756000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1716000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1606000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1710000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1718000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1688000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1806000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1763000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1853000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1626000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1779000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1672000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1479000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1980000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1023000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2109000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2769000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1719000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2077000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1426000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2709000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3530000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2697000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3188000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2106000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1649000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1630000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2345000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3130000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2771000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2790000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1700000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2673000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1272000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7973000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7635000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7355000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7007000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7473000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7130000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7376000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7786000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7915000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7602000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7610000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7700000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8220000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8281000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8496000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8982000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9611000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9289000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9875000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9475000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10769000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10531000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11164000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12247000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11394000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11843000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10411000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11469000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11534000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10996000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11613000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11027000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11825000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12691000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12089000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13164000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12103000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11751000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12322000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13674000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14107000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14452000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14028000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14322000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14830000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14215000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18161000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18495000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18698000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19668000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19103000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18497000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20363000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20840000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21617000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21037000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21602000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22288000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22731000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23515000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>24616000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24473000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24562000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23812000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25955000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25828000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26691000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26792000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28949000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4945000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4687000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4846000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4765000</v>
       </c>
-      <c r="G62" s="3">
-        <v>4743000</v>
-      </c>
       <c r="H62" s="3">
+        <v>4841000</v>
+      </c>
+      <c r="I62" s="3">
         <v>4702000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4745000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4346000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3778000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3538000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3591000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3652000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3684000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3527000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3800000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3947000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4171000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4402000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3766000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4177000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3876000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4305000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4498000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5345,8 +5493,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5437,8 +5588,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5529,100 +5683,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35973000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35158000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36043000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35595000</v>
       </c>
-      <c r="G66" s="3">
-        <v>36109000</v>
-      </c>
       <c r="H66" s="3">
+        <v>36207000</v>
+      </c>
+      <c r="I66" s="3">
         <v>35484000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36895000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37715000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37388000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37384000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38871000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39004000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40614000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40144000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41139000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41799000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>43498000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>43455000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45301000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>45122000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>45976000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47331000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>49092000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5655,8 +5815,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5747,8 +5908,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5839,8 +6003,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5905,19 +6072,19 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>3825000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>3760000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AC70" s="3">
         <v>3620000</v>
@@ -5931,8 +6098,11 @@
       <c r="AF70" s="3">
         <v>3620000</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>3620000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6023,100 +6193,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13534000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="G72" s="3">
-        <v>-12882000</v>
-      </c>
       <c r="H72" s="3">
+        <v>-12975000</v>
+      </c>
+      <c r="I72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6207,8 +6383,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6299,8 +6478,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6391,100 +6573,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7506000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6930000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7052000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7861000</v>
       </c>
-      <c r="G76" s="3">
-        <v>7897000</v>
-      </c>
       <c r="H76" s="3">
+        <v>7804000</v>
+      </c>
+      <c r="I76" s="3">
         <v>8768000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9037000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9344000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10278000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10467000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10324000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10000000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10026000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9593000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13852000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13531000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13972000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13791000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14123000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14732000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14707000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13905000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14178000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6575,197 +6763,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E81" s="3">
         <v>80000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-863000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-205000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1221000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-1314000</v>
+      </c>
+      <c r="I81" s="3">
         <v>56000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-232000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-955000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-159000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>292000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>207000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>77000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>150000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>140000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>69000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>109000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-314000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-689000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-105000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-283000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-241000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>530000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>580000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6798,100 +6995,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E83" s="3">
         <v>283000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>304000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>306000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>321000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>358000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>323000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>320000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>329000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>305000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>376000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>395000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>381000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>382000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>399000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>416000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>413000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>450000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>443000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>382000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>474000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>479000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>507000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>528000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>527000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>577000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>480000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>332000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6982,8 +7183,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7074,8 +7278,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7166,8 +7373,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7258,8 +7468,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7350,100 +7563,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1184000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>324000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-145000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>973000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>544000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>122000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>456000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>529000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>218000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-405000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>331000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>307000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>273000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>305000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>538000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>325000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-227000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>112000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>367000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>421000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>162000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>741000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>470000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7476,100 +7695,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-149000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-119000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-139000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-142000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-122000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-127000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-157000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-153000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-146000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-113000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-150000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-176000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-131000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-128000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-119000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-169000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-112000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-125000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-213000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-139000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-136000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7660,8 +7883,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7752,100 +7978,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E94" s="3">
         <v>184000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>302000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>181000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>168000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>147000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>180000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>161000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>246000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>288000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>481000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>508000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>141000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>157000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>313000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>252000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>430000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>224000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>429000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>272000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>74000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>347000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>406000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>744000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7878,8 +8110,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7950,28 +8183,31 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AE96" s="3">
         <v>-346000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8062,8 +8298,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8154,8 +8393,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8246,8 +8488,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8255,271 +8500,280 @@
         <v>-576000</v>
       </c>
       <c r="E100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-55000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-706000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-711000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-440000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-338000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-501000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-493000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-125000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-241000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-35000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-189000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-499000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-705000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-33000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-77000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>146000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-84000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-123000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-62000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-48000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-31000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-44000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>18000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>15000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-28000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-12000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>25000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-35000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-49000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>11000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>18000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>28000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>977000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-420000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>494000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-658000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>576000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>167000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-159000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>153000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-391000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>693000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-434000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>350000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-575000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>598000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-171000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>734000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-924000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>192000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>191000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-93000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>443000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>455000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>283000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>81000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,421 +656,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3819000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4457000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3850000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3878000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3661000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3884000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3595000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3786000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3661000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4100000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3887000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3910000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3982000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4453000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3978000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3870000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4357000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3991000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4093000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4177000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4149000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4559000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4529000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2048000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1960000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1936000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1959000</v>
       </c>
-      <c r="G9" s="3">
-        <v>2015000</v>
-      </c>
       <c r="H9" s="3">
+        <v>2079000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1784000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1885000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1958000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1859000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1975000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1989000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1987000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2063000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2372000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2128000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2091000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2279000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2033000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="V9" s="3">
-        <v>2258000</v>
       </c>
       <c r="W9" s="3">
         <v>2258000</v>
       </c>
       <c r="X9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="Y9" s="3">
         <v>2693000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2552000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1771000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2497000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1914000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1919000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1646000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1582000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2100000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1710000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1828000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1802000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2125000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1898000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1923000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1919000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2081000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1850000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1779000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2078000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1958000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1864000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1919000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1891000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1866000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1977000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1104,103 +1116,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E12" s="3">
         <v>227000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>253000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>240000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>234000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>210000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>175000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>228000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>225000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>249000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>222000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>243000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>254000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>296000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>238000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>242000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>221000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>232000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>487000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>276000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>261000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>295000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>311000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>290000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>317000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>346000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>531000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>469000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>432000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>684000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1294,103 +1310,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>859000</v>
+      </c>
+      <c r="E14" s="3">
         <v>652000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>465000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1449000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>585000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1978000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>321000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1683000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1502000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>893000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>183000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>247000</v>
+      </c>
+      <c r="P14" s="3">
+        <v>360000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>374000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>5077000</v>
+      </c>
+      <c r="S14" s="3">
+        <v>516000</v>
+      </c>
+      <c r="T14" s="3">
+        <v>764000</v>
+      </c>
+      <c r="U14" s="3">
         <v>561000</v>
       </c>
-      <c r="H14" s="3">
-        <v>1978000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>321000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1683000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1502000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>893000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>183000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>247000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>360000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>374000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>5077000</v>
-      </c>
-      <c r="R14" s="3">
-        <v>516000</v>
-      </c>
-      <c r="S14" s="3">
-        <v>764000</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
+        <v>832000</v>
+      </c>
+      <c r="W14" s="3">
+        <v>1323000</v>
+      </c>
+      <c r="X14" s="3">
         <v>561000</v>
       </c>
-      <c r="U14" s="3">
-        <v>832000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1323000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>561000</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3804000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1165000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>855000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>520000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>205000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,44 +1431,44 @@
       <c r="H15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="3">
         <v>20000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>27000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>31000</v>
       </c>
       <c r="Q15" s="3">
         <v>31000</v>
       </c>
       <c r="R15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="S15" s="3">
         <v>30000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>35000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>34000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>35000</v>
       </c>
       <c r="V15" s="3">
         <v>35000</v>
@@ -1455,28 +1477,28 @@
         <v>35000</v>
       </c>
       <c r="X15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>24000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>51000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>41000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>46000</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
-      </c>
       <c r="AC15" s="3">
         <v>0</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>11</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>11</v>
@@ -1484,8 +1506,11 @@
       <c r="AG15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1516,198 +1541,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4037000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3735000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3495000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4524000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3659000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3674000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4837000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3176000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4735000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4374000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4022000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3264000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3328000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3548000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4048000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8320000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3697000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4166000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3843000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4174000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4821000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4015000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7709000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4513000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E18" s="3">
         <v>722000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>355000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-646000</v>
       </c>
-      <c r="G18" s="3">
-        <v>2000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-953000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>419000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-949000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-713000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>78000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>623000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>582000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>434000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>405000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>173000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>191000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>148000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-81000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-644000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>134000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>378000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>895000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1741,239 +1773,246 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E20" s="3">
         <v>57000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-33000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-52000</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-9000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-73000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-51000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>124000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>17000</v>
       </c>
       <c r="S20" s="3">
         <v>17000</v>
       </c>
       <c r="T20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="U20" s="3">
         <v>22000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>20000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>11000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>14000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>30000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>290000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1045000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>605000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-398000</v>
       </c>
-      <c r="G21" s="3">
-        <v>306000</v>
-      </c>
       <c r="H21" s="3">
+        <v>268000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-656000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>717000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-577000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-410000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>325000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>943000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>853000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>759000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>773000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>572000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>607000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>586000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>340000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-174000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>586000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>501000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>460000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>865000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E22" s="3">
         <v>306000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>247000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>216000</v>
       </c>
-      <c r="G22" s="3">
-        <v>260000</v>
-      </c>
       <c r="H22" s="3">
+        <v>236000</v>
+      </c>
+      <c r="I22" s="3">
         <v>237000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>230000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>225000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>238000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>180000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>232000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>240000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>239000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>241000</v>
       </c>
       <c r="Q22" s="3">
         <v>241000</v>
@@ -1985,239 +2024,248 @@
         <v>241000</v>
       </c>
       <c r="T22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="U22" s="3">
         <v>209000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>219000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>226000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>227000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>231000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>240000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>231000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>218000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>221000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>219000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>526000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-467000</v>
+      </c>
+      <c r="E23" s="3">
         <v>473000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>75000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-914000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-258000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-272000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>166000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-971000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-175000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>382000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>308000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>144000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>137000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-51000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-33000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-39000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-292000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-850000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-84000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-213000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>119000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>688000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E24" s="3">
         <v>41000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-12000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-16000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-19000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>149000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>107000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-900000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-24000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>76000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>98000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>62000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>16000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-104000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-59000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-119000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-179000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-236000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>46000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>54000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>57000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2311,198 +2359,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-415000</v>
+      </c>
+      <c r="E26" s="3">
         <v>432000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>87000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-898000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-239000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-253000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>59000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-260000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-973000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-151000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>306000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>210000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>82000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>158000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>53000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>26000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>80000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-303000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-671000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-93000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-187000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>613000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>634000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E27" s="3">
         <v>429000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>80000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-863000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-205000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>56000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-232000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-955000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-159000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>292000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>207000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>77000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>150000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>140000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>69000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>109000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-314000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-689000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-105000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>530000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>580000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2596,8 +2653,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2643,8 +2703,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>11</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>11</v>
@@ -2661,11 +2721,11 @@
       <c r="W29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>11</v>
@@ -2673,11 +2733,11 @@
       <c r="AA29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>11</v>
@@ -2691,8 +2751,11 @@
       <c r="AG29" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2786,8 +2849,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2881,198 +2947,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-57000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>33000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>52000</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I32" s="3">
         <v>9000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>73000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>51000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>27000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-17000</v>
       </c>
       <c r="S32" s="3">
         <v>-17000</v>
       </c>
       <c r="T32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="U32" s="3">
         <v>-22000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-20000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>40000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>56000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>777000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E33" s="3">
         <v>429000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>80000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-863000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-205000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>56000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-232000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-955000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-159000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>292000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>207000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>77000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>150000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>140000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>69000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>109000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-314000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-689000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-105000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>530000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>580000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3166,203 +3241,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E35" s="3">
         <v>429000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>80000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-863000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-205000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>56000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-232000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-955000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-159000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>292000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>207000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>77000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>150000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>140000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>69000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>109000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-314000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-689000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-105000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>530000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>580000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3396,8 +3480,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3431,103 +3516,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2991000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3226000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2249000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2669000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2143000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2801000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2225000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2058000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2175000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2165000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2045000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2436000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1743000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2177000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1827000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2402000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1804000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1975000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1241000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2165000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1973000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1782000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1875000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>963000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>680000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>599000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>900000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>988000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3621,388 +3710,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3456000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3408000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3385000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3539000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3435000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3696000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3730000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4471000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4253000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4529000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4046000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4488000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4572000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4581000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4385000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4545000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5189000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5676000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5254000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5260000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5108000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5822000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5665000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3949000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4022000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4051000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4109000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4118000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3833000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3859000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4049000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4012000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3818000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4167000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4362000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4406000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4403000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4516000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4361000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4290000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4422000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4636000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4850000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4782000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4731000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4866000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1901000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1830000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1740000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1771000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1805000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1721000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1639000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1586000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2011000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2061000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1896000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1536000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1680000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1844000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1432000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1473000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1601000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1391000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1411000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1530000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1568000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1459000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1475000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12297000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12486000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11425000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12088000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11501000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12051000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11453000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12164000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12451000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12573000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12154000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12822000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12401000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13005000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12160000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12781000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12884000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13464000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12542000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13805000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13431000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13794000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13881000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4096,198 +4200,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5982000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6147000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6028000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6130000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6171000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6158000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5990000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6181000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6396000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6477000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6547000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6658000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6641000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6855000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6709000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6611000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6710000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6950000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7111000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7232000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7302000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6868000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7101000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22063000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22564000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22410000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22856000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23763000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23903000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24826000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25537000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27102000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>27506000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28011000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28541000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28747000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>29547000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>29536000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34556000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>34746000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36078000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>36535000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>37348000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>38013000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>38922000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>42930000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4381,8 +4494,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4476,103 +4592,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2431000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2283000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2225000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2021000</v>
       </c>
       <c r="G52" s="3">
         <v>2021000</v>
       </c>
       <c r="H52" s="3">
+        <v>2021000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1899000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1983000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1110000</v>
       </c>
       <c r="L52" s="3">
         <v>1110000</v>
       </c>
       <c r="M52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="N52" s="3">
         <v>1139000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1174000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1215000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1233000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1332000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1043000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>990000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>978000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1058000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1039000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1108000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1099000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1149000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4666,103 +4788,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42773000</v>
+      </c>
+      <c r="E54" s="3">
         <v>43480000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42088000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43095000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43456000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44011000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44252000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45932000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47059000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47666000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47851000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>49195000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>49004000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>50640000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49737000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>54991000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>55330000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57470000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57246000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59424000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59854000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60683000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>65061000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4796,8 +4924,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4831,578 +4960,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2439000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2602000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2280000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2508000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2381000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1887000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1635000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1901000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1750000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1686000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1514000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1551000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1692000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1756000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1716000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1606000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1710000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1718000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1688000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1806000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1763000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1853000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1626000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3060000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1672000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1479000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1980000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1023000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2109000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2769000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1719000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2077000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1426000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2709000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3530000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2697000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3188000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2106000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1649000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1630000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2345000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3130000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2771000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2790000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1700000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2673000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8293000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7973000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7635000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7355000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7007000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7473000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7130000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7376000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7786000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7915000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7602000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7610000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7700000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8220000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8281000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8496000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8982000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9611000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9289000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9875000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9475000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10769000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10531000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13792000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12247000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11394000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11843000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10411000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11469000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11534000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10996000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11613000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11027000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11825000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12691000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12089000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13164000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12103000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11751000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12322000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13674000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14107000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14452000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14028000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14322000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14830000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16584000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18161000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18495000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18698000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19668000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19103000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18497000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20363000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20840000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21617000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21037000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21602000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22288000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22731000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23515000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24616000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24473000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24562000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23812000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25955000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>25828000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26691000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26792000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4854000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4945000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4687000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4846000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4765000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4841000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4702000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4745000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4346000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3778000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3538000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3591000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3652000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3684000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3527000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3800000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3947000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4171000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4402000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3766000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4177000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3876000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4305000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5496,8 +5644,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5591,8 +5742,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5686,103 +5840,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35495000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35973000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35158000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36043000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35595000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36207000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35484000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36895000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37715000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37388000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37384000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38871000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39004000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40614000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40144000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41139000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>41799000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>43498000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43455000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>45301000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>45122000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45976000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47331000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5816,8 +5976,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5911,8 +6072,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6006,8 +6170,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6075,19 +6242,19 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>3825000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AD70" s="3">
         <v>3620000</v>
@@ -6101,8 +6268,11 @@
       <c r="AG70" s="3">
         <v>3620000</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>3620000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6196,103 +6366,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13673000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6386,8 +6562,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6481,8 +6660,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6576,103 +6758,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7278000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7506000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6930000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7052000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7861000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7804000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8768000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9037000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9344000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10278000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10467000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10324000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10000000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10026000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9593000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13852000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13531000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13972000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13791000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14123000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14732000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14707000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13905000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6766,203 +6954,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E81" s="3">
         <v>429000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>80000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-863000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-205000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>56000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-232000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-955000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-159000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>292000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>207000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>77000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>150000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>140000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>69000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>109000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-314000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-689000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-105000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>530000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>580000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6996,103 +7193,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E83" s="3">
         <v>266000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>283000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>304000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>306000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>321000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>358000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>323000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>320000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>329000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>305000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>376000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>395000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>381000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>382000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>399000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>416000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>413000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>450000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>443000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>382000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>474000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>479000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>507000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>528000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>527000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>577000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>480000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>332000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7186,8 +7387,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7281,8 +7485,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7376,8 +7583,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7471,8 +7681,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7566,103 +7779,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1184000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>324000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-145000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>973000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>544000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>122000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-49000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>456000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>529000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>218000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-405000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>331000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>307000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>273000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>305000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>538000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>325000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-227000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>112000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>367000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>421000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>162000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>741000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>470000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7696,103 +7915,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-119000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-149000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-119000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-139000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-142000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-122000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-127000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-157000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-153000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-146000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-113000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-150000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-176000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-143000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-131000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-128000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-119000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-169000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-112000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-125000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-213000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-139000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7886,8 +8109,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7981,103 +8207,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E94" s="3">
         <v>301000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>184000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>302000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>181000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>168000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>147000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>180000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>161000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>246000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>288000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>481000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>508000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>141000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>157000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>313000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>252000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>430000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>224000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>429000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>272000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>74000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>347000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>406000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>744000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8111,8 +8343,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8186,28 +8419,31 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AF96" s="3">
         <v>-346000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8301,8 +8537,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8396,8 +8635,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8491,289 +8733,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-576000</v>
+        <v>-151000</v>
       </c>
       <c r="E100" s="3">
         <v>-576000</v>
       </c>
       <c r="F100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-55000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-706000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-711000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-440000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-338000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-501000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-493000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-125000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-700000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-241000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-35000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-189000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-499000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-705000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E101" s="3">
         <v>68000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-33000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-77000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>146000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-84000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-123000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-62000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-48000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-31000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-44000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>18000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>15000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-28000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-12000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>25000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>18000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>28000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="E102" s="3">
         <v>977000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-420000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>494000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-658000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>576000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>167000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-159000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>153000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-391000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>693000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-434000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>350000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-575000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>598000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-171000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>734000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-924000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>192000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>191000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-93000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>443000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>455000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>283000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>81000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,433 +656,445 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4164000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3819000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4457000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3850000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3878000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3661000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3884000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3595000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3786000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3661000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4100000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3887000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3910000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3982000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4453000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3978000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3870000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4357000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3991000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4093000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4177000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4149000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4559000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2081000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2048000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1960000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1936000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1959000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2079000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1784000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1885000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1958000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1859000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1975000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1989000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1987000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2063000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2372000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2128000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2091000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2279000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2033000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="W9" s="3">
-        <v>2258000</v>
       </c>
       <c r="X9" s="3">
         <v>2258000</v>
       </c>
       <c r="Y9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="Z9" s="3">
         <v>2693000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2083000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1771000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2497000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1914000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1919000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1582000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2100000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1710000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1828000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1802000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2125000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1898000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1923000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1919000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2081000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1850000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1779000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2078000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1958000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1864000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1919000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1891000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1866000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1117,106 +1129,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E12" s="3">
         <v>242000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>227000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>253000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>240000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>234000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>210000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>175000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>228000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>225000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>249000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>222000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>243000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>254000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>296000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>238000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>242000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>221000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>232000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>487000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>276000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>261000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>295000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>311000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>290000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>317000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>346000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>531000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>469000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>432000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>684000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,106 +1329,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E14" s="3">
         <v>859000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>652000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>465000</v>
       </c>
-      <c r="G14" s="3">
-        <v>1449000</v>
-      </c>
       <c r="H14" s="3">
+        <v>1459000</v>
+      </c>
+      <c r="I14" s="3">
         <v>585000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1978000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>321000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1683000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1502000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>893000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>183000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>247000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>360000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>374000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5077000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>516000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>764000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>561000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>832000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1323000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>561000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3804000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>855000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>520000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>205000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1434,44 +1456,44 @@
       <c r="I15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="3">
         <v>20000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>22000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>31000</v>
       </c>
       <c r="R15" s="3">
         <v>31000</v>
       </c>
       <c r="S15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="T15" s="3">
         <v>30000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>35000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>35000</v>
       </c>
       <c r="W15" s="3">
         <v>35000</v>
@@ -1480,28 +1502,28 @@
         <v>35000</v>
       </c>
       <c r="Y15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>24000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>51000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>41000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>46000</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
       <c r="AD15" s="3">
         <v>0</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>11</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>11</v>
@@ -1509,8 +1531,11 @@
       <c r="AH15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1542,204 +1567,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4169000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4037000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3735000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3495000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4524000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4532000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3674000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4837000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3176000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4735000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4374000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4022000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3264000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3328000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3548000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4048000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8320000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3697000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4166000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3843000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4174000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4821000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4015000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7709000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-218000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>722000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>355000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-646000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-654000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-953000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>419000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-949000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-713000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>78000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>623000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>582000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>434000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>405000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>173000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>191000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>148000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-81000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-644000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>134000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>378000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>895000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1774,204 +1806,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-16000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>57000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-33000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-52000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-23000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-20000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-73000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-34000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-27000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>124000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>17000</v>
       </c>
       <c r="T20" s="3">
         <v>17000</v>
       </c>
       <c r="U20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="V20" s="3">
         <v>22000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>11000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>14000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>30000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>290000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E21" s="3">
         <v>38000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1045000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>605000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-398000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-383000</v>
+      </c>
+      <c r="I21" s="3">
         <v>268000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-656000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>717000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-577000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-410000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>325000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>943000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>853000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>759000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>773000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>572000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>607000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>586000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>340000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-174000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>586000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>501000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>460000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>865000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1979,43 +2018,43 @@
         <v>233000</v>
       </c>
       <c r="E22" s="3">
+        <v>233000</v>
+      </c>
+      <c r="F22" s="3">
         <v>306000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>247000</v>
       </c>
-      <c r="G22" s="3">
-        <v>216000</v>
-      </c>
       <c r="H22" s="3">
+        <v>240000</v>
+      </c>
+      <c r="I22" s="3">
         <v>236000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>237000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>230000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>225000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>238000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>180000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>232000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>240000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>239000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>241000</v>
       </c>
       <c r="R22" s="3">
         <v>241000</v>
@@ -2027,245 +2066,254 @@
         <v>241000</v>
       </c>
       <c r="U22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="V22" s="3">
         <v>209000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>219000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>226000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>227000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>231000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>240000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>231000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>218000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>221000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>219000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>526000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-467000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>473000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>75000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-923000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-272000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1199000</v>
+      </c>
+      <c r="K23" s="3">
+        <v>166000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1160000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-971000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-175000</v>
+      </c>
+      <c r="O23" s="3">
+        <v>382000</v>
+      </c>
+      <c r="P23" s="3">
+        <v>308000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>144000</v>
+      </c>
+      <c r="R23" s="3">
+        <v>137000</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-4459000</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="U23" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-292000</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-850000</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-3387000</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>-213000</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>-250000</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>1254000</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-13208000</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>119000</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>-5978000</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>688000</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-914000</v>
       </c>
-      <c r="H23" s="3">
-        <v>-272000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1199000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>166000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1160000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-971000</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-175000</v>
-      </c>
-      <c r="N23" s="3">
-        <v>382000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>308000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>144000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>137000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-4459000</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-51000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-33000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-292000</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-850000</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-84000</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-3387000</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-213000</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-250000</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>1254000</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-13208000</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>119000</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-5978000</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>688000</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-914000</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>630000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-52000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-12000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-19000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>149000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>107000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-900000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-24000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>76000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>98000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>62000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-104000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-59000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-119000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-179000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-236000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>54000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>57000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2362,204 +2410,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-876000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-415000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>432000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>87000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-898000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-907000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-253000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>59000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-260000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-973000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-151000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>306000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>210000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>158000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>53000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>80000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-303000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-671000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-93000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>613000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>634000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-846000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-139000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>429000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>80000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-863000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-873000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-219000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>56000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-232000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-955000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-159000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>292000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>207000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>77000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>150000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>140000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>69000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>109000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-314000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-689000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-105000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>530000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>580000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2656,8 +2713,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2706,8 +2766,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>11</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>11</v>
@@ -2724,11 +2784,11 @@
       <c r="X29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>11</v>
@@ -2736,11 +2796,11 @@
       <c r="AB29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>11</v>
@@ -2754,8 +2814,11 @@
       <c r="AH29" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2852,8 +2915,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2950,204 +3016,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E32" s="3">
         <v>16000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-57000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>33000</v>
       </c>
-      <c r="G32" s="3">
-        <v>52000</v>
-      </c>
       <c r="H32" s="3">
+        <v>29000</v>
+      </c>
+      <c r="I32" s="3">
         <v>23000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>20000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>73000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>34000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>51000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>27000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-17000</v>
       </c>
       <c r="T32" s="3">
         <v>-17000</v>
       </c>
       <c r="U32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="V32" s="3">
         <v>-22000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>40000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>56000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>777000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-846000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-139000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>429000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>80000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-863000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-873000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-219000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>56000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-232000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-955000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-159000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>292000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>207000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>77000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>150000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>140000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>69000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>109000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-314000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-689000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-105000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>530000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>580000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3244,209 +3319,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-846000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-139000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>429000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>80000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-863000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-873000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-219000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>56000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-232000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-955000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-159000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>292000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>207000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>77000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>150000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>140000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>69000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>109000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-314000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-689000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-105000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>530000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>580000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3481,8 +3565,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3517,106 +3602,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2991000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3226000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2249000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2669000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2143000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2801000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2225000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2058000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2175000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2165000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2045000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2436000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1743000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2177000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1827000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2402000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1804000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1975000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1241000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2165000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1973000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1782000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>963000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>680000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>599000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>900000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>988000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3713,400 +3802,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3766000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3456000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3408000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3385000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3539000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3435000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3696000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3730000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4471000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4253000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4529000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4046000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4488000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4572000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4581000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4385000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4545000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5189000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5676000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5254000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5260000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5108000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5822000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3927000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3949000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4022000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4051000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4109000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4118000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3833000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3859000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4049000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4012000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3818000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4167000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4362000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4406000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4403000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4516000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4361000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4290000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4422000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4636000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4850000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4782000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4731000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1681000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1901000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1830000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1740000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1771000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1805000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1721000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1639000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1586000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2011000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2061000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1896000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1536000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1680000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1844000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1432000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1473000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1601000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1391000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1411000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1530000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1568000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1459000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11632000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12297000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12486000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11425000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12088000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11501000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12051000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11453000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12164000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12451000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12573000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12154000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12822000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12401000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13005000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12160000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12781000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12884000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13464000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12542000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13805000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13431000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13794000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4203,204 +4307,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5931000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5982000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6147000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6028000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6130000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6171000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6158000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5990000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6181000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6396000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6477000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6547000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6658000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6641000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6855000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6709000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6611000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6710000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6950000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7111000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7232000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7302000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6868000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21341000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22063000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22564000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22410000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22856000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23763000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23903000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24826000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25537000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>27102000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27506000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28011000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28541000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>28747000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>29547000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>29536000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>34556000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>34746000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>36078000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>36535000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>37348000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>38013000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>38922000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4497,8 +4610,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4595,106 +4711,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2434000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2431000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2283000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2225000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2021000</v>
       </c>
       <c r="H52" s="3">
         <v>2021000</v>
       </c>
       <c r="I52" s="3">
+        <v>2021000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1899000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1983000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1110000</v>
       </c>
       <c r="M52" s="3">
         <v>1110000</v>
       </c>
       <c r="N52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="O52" s="3">
         <v>1139000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1174000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1215000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1233000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1332000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1043000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>990000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>978000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1058000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1039000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1108000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1099000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4791,106 +4913,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41338000</v>
+      </c>
+      <c r="E54" s="3">
         <v>42773000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43480000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42088000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43095000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43456000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44011000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44252000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45932000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47059000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47666000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47851000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>49195000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49004000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>50640000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>49737000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>54991000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>55330000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57470000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>57246000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59424000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59854000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60683000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4925,8 +5053,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4961,596 +5090,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2366000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2439000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2602000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2280000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2508000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2381000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1887000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1635000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1901000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1750000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1686000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1514000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1551000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1692000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1756000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1716000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1606000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1710000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1718000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1688000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1806000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1763000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1853000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3060000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1672000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1479000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1980000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1023000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2109000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2769000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1719000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2077000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1426000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2709000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3530000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2697000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3188000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2106000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1649000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1630000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2345000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3130000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2771000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2790000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1700000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8577000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8293000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7973000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7635000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7355000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7007000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7473000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7130000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7376000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7786000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7915000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7602000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7610000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7700000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8220000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8281000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8496000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8982000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9611000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9289000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9875000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9475000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10769000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13037000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13792000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12247000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11394000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11843000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10411000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11469000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11534000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10996000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11613000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11027000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11825000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12691000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12089000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13164000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12103000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11751000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12322000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13674000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14107000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14452000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14028000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14322000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16547000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16584000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18161000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18495000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18698000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19668000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19103000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18497000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20363000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20840000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21617000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21037000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21602000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22288000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22731000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23515000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24616000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24473000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24562000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23812000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>25955000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>25828000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26691000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5191000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4854000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4945000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4687000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4846000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4765000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4841000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4702000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4745000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4346000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3778000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3538000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3591000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3652000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3684000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3527000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3800000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3947000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4171000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4402000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3766000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4177000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3876000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5647,8 +5795,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5745,8 +5896,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5843,106 +5997,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34979000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35495000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35973000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35158000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36043000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35595000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36207000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35484000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36895000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37715000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37388000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37384000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38871000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39004000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40614000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40144000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>41139000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>41799000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43498000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43455000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>45301000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45122000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45976000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5977,8 +6137,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6075,8 +6236,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6173,8 +6337,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6245,19 +6412,19 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AE70" s="3">
         <v>3620000</v>
@@ -6271,8 +6438,11 @@
       <c r="AH70" s="3">
         <v>3620000</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>3620000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6369,106 +6539,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14519000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6565,8 +6741,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6663,8 +6842,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6761,106 +6943,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6359000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7278000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7506000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6930000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7052000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7861000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7804000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8768000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9037000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9344000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10278000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10467000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10324000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10000000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10026000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9593000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13852000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13531000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13972000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13791000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14123000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14732000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14707000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6957,209 +7145,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-846000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-139000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>429000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>80000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-863000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-873000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-219000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>56000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-232000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-955000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-159000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>292000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>207000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>77000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>150000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>140000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>69000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>109000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-314000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-689000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-105000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>530000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>580000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7194,106 +7391,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E83" s="3">
         <v>272000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>266000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>283000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>304000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>306000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>321000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>358000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>323000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>320000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>329000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>305000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>376000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>395000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>381000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>382000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>399000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>416000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>413000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>450000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>443000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>382000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>474000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>479000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>507000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>528000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>527000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>577000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>480000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>332000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7390,8 +7591,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7488,8 +7692,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7586,8 +7793,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7684,8 +7894,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7782,106 +7995,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-125000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1184000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>324000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-145000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>973000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>544000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>122000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-49000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>456000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>529000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>218000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-405000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>331000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>307000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>273000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>305000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>538000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>325000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-227000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>112000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>367000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>421000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>162000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>741000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>470000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7916,106 +8135,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-124000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-119000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-149000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-119000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-139000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-142000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-122000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-127000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-157000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-153000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-146000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-113000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-150000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-176000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-143000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-131000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-128000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-119000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-169000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-112000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-125000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-213000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8112,8 +8335,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8210,106 +8436,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E94" s="3">
         <v>144000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>301000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>184000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>302000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>181000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>168000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>147000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>180000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>161000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>246000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>288000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>481000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>508000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>141000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>157000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>313000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>252000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>430000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>224000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>429000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>272000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>74000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>347000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>406000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>744000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8344,8 +8576,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8422,28 +8655,31 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AG96" s="3">
         <v>-346000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8540,8 +8776,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8638,8 +8877,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8736,298 +8978,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-966000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-576000</v>
       </c>
       <c r="F100" s="3">
         <v>-576000</v>
       </c>
       <c r="G100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="H100" s="3">
         <v>-55000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-706000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-711000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-440000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-338000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-501000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-493000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-125000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-700000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-241000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-35000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-189000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-499000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-104000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>68000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-33000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-77000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>146000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-84000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-123000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-62000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-48000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-31000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>18000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>15000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-28000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>25000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>11000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>18000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>7000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>28000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-733000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-236000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>977000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-420000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>494000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-658000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>576000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>167000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-159000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>52000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>153000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-391000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>693000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-434000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>350000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-575000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>598000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-171000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>734000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-924000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>192000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>191000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-93000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>443000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>455000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>283000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>81000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,445 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4332000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4164000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3819000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4457000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3850000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3878000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3661000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3884000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3595000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3786000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3661000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4100000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3887000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3910000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3982000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4453000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3978000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3870000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4357000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3991000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4093000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4177000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4149000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4559000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2081000</v>
+        <v>2183000</v>
       </c>
       <c r="E9" s="3">
+        <v>2140000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2048000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1960000</v>
-      </c>
       <c r="G9" s="3">
-        <v>1936000</v>
+        <v>2041000</v>
       </c>
       <c r="H9" s="3">
-        <v>1959000</v>
+        <v>1999000</v>
       </c>
       <c r="I9" s="3">
+        <v>2082000</v>
+      </c>
+      <c r="J9" s="3">
         <v>2079000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1784000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1885000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1958000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1859000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1975000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1989000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1987000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2063000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2372000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2128000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2091000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2279000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2033000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>2258000</v>
       </c>
       <c r="Y9" s="3">
         <v>2258000</v>
       </c>
       <c r="Z9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="AA9" s="3">
         <v>2693000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2083000</v>
+        <v>2149000</v>
       </c>
       <c r="E10" s="3">
+        <v>2024000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1771000</v>
       </c>
-      <c r="F10" s="3">
-        <v>2497000</v>
-      </c>
       <c r="G10" s="3">
-        <v>1914000</v>
+        <v>2416000</v>
       </c>
       <c r="H10" s="3">
+        <v>1851000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1796000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1582000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2100000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1710000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>2125000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1898000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1923000</v>
+      </c>
+      <c r="R10" s="3">
         <v>1919000</v>
       </c>
-      <c r="I10" s="3">
-        <v>1582000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2100000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1710000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1828000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1802000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2125000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1898000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1923000</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
+        <v>2081000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1779000</v>
+      </c>
+      <c r="V10" s="3">
+        <v>2078000</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1864000</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1919000</v>
       </c>
-      <c r="R10" s="3">
-        <v>2081000</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1850000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1779000</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2078000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1958000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1864000</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1919000</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1891000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1866000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1130,109 +1142,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E12" s="3">
         <v>269000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>242000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>227000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>253000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>240000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>234000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>210000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>175000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>228000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>225000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>249000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>222000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>243000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>254000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>296000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>238000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>242000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>221000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>232000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>487000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>276000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>261000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>295000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>311000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>290000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>317000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>346000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>531000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>469000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>432000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>684000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1332,171 +1348,177 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>883000</v>
+        <v>1053000</v>
       </c>
       <c r="E14" s="3">
-        <v>859000</v>
+        <v>823000</v>
       </c>
       <c r="F14" s="3">
-        <v>652000</v>
+        <v>877000</v>
       </c>
       <c r="G14" s="3">
-        <v>465000</v>
+        <v>529000</v>
       </c>
       <c r="H14" s="3">
-        <v>1459000</v>
+        <v>416000</v>
       </c>
       <c r="I14" s="3">
-        <v>585000</v>
+        <v>1324000</v>
       </c>
       <c r="J14" s="3">
+        <v>512000</v>
+      </c>
+      <c r="K14" s="3">
         <v>1978000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>321000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1683000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1502000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>893000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>183000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>247000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>360000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>374000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5077000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>516000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>764000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>561000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>832000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1323000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>561000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3804000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>855000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>520000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>205000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>272000</v>
+      </c>
+      <c r="G15" s="3">
+        <v>266000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>283000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>300000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>304000</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>24000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>25000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>27000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>31000</v>
       </c>
       <c r="S15" s="3">
         <v>31000</v>
       </c>
       <c r="T15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="U15" s="3">
         <v>30000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>35000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>35000</v>
       </c>
       <c r="X15" s="3">
         <v>35000</v>
@@ -1505,28 +1527,28 @@
         <v>35000</v>
       </c>
       <c r="Z15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>24000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>51000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>41000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>46000</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
       <c r="AE15" s="3">
         <v>0</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>11</v>
+      <c r="AG15" s="3">
+        <v>0</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>11</v>
@@ -1534,8 +1556,11 @@
       <c r="AI15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1568,210 +1593,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4169000</v>
+        <v>3328000</v>
       </c>
       <c r="E17" s="3">
-        <v>4037000</v>
+        <v>3347000</v>
       </c>
       <c r="F17" s="3">
-        <v>3735000</v>
+        <v>3159000</v>
       </c>
       <c r="G17" s="3">
-        <v>3495000</v>
+        <v>3207000</v>
       </c>
       <c r="H17" s="3">
-        <v>4532000</v>
+        <v>3089000</v>
       </c>
       <c r="I17" s="3">
-        <v>3674000</v>
+        <v>3208000</v>
       </c>
       <c r="J17" s="3">
+        <v>3162000</v>
+      </c>
+      <c r="K17" s="3">
         <v>4837000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3176000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4735000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4374000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4022000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3264000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3328000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3548000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4048000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8320000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3697000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4166000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3843000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4174000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4821000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4015000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7709000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5000</v>
+        <v>1004000</v>
       </c>
       <c r="E18" s="3">
-        <v>-218000</v>
+        <v>817000</v>
       </c>
       <c r="F18" s="3">
-        <v>722000</v>
+        <v>660000</v>
       </c>
       <c r="G18" s="3">
-        <v>355000</v>
+        <v>1250000</v>
       </c>
       <c r="H18" s="3">
-        <v>-654000</v>
+        <v>761000</v>
       </c>
       <c r="I18" s="3">
-        <v>-13000</v>
+        <v>670000</v>
       </c>
       <c r="J18" s="3">
+        <v>499000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-953000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>419000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-949000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-713000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>78000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>623000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>582000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>434000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>405000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>173000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>191000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>148000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-81000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-644000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>134000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>378000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>895000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1807,257 +1839,264 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-8000</v>
+        <v>47000</v>
       </c>
       <c r="E20" s="3">
-        <v>-16000</v>
+        <v>6000</v>
       </c>
       <c r="F20" s="3">
-        <v>57000</v>
+        <v>12000</v>
       </c>
       <c r="G20" s="3">
-        <v>-33000</v>
+        <v>-13000</v>
       </c>
       <c r="H20" s="3">
-        <v>-29000</v>
+        <v>40000</v>
       </c>
       <c r="I20" s="3">
+        <v>43000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="L20" s="3">
         <v>-23000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="P20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3">
-        <v>-23000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>14000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-73000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-51000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-27000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>124000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>17000</v>
       </c>
       <c r="U20" s="3">
         <v>17000</v>
       </c>
       <c r="V20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="W20" s="3">
         <v>22000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>11000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>14000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>30000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>290000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>246000</v>
+        <v>1216000</v>
       </c>
       <c r="E21" s="3">
-        <v>38000</v>
+        <v>1070000</v>
       </c>
       <c r="F21" s="3">
-        <v>1045000</v>
+        <v>920000</v>
       </c>
       <c r="G21" s="3">
-        <v>605000</v>
+        <v>1529000</v>
       </c>
       <c r="H21" s="3">
-        <v>-383000</v>
+        <v>1004000</v>
       </c>
       <c r="I21" s="3">
-        <v>268000</v>
+        <v>927000</v>
       </c>
       <c r="J21" s="3">
+        <v>805000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-656000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>717000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-577000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-410000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>325000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>943000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>853000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>759000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>773000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>572000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>607000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>586000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>340000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-174000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>586000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>501000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>460000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>865000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>233000</v>
+        <v>225000</v>
       </c>
       <c r="E22" s="3">
         <v>233000</v>
       </c>
       <c r="F22" s="3">
-        <v>306000</v>
+        <v>242000</v>
       </c>
       <c r="G22" s="3">
-        <v>247000</v>
+        <v>328000</v>
       </c>
       <c r="H22" s="3">
         <v>240000</v>
       </c>
       <c r="I22" s="3">
-        <v>236000</v>
+        <v>226000</v>
       </c>
       <c r="J22" s="3">
+        <v>261000</v>
+      </c>
+      <c r="K22" s="3">
         <v>237000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>230000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>225000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>238000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>180000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>232000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>240000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>239000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>241000</v>
       </c>
       <c r="S22" s="3">
         <v>241000</v>
@@ -2069,251 +2108,260 @@
         <v>241000</v>
       </c>
       <c r="V22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="W22" s="3">
         <v>209000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>219000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>226000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>227000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>231000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>240000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>231000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>218000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>221000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>219000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>526000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-246000</v>
+        <v>-321000</v>
       </c>
       <c r="E23" s="3">
-        <v>-467000</v>
+        <v>-245000</v>
       </c>
       <c r="F23" s="3">
-        <v>473000</v>
+        <v>-471000</v>
       </c>
       <c r="G23" s="3">
-        <v>75000</v>
+        <v>474000</v>
       </c>
       <c r="H23" s="3">
+        <v>65000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-923000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-272000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>166000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-971000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-175000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>382000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>308000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>144000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>137000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-51000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-33000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-39000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-292000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-850000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-213000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>119000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>688000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E24" s="3">
         <v>630000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-52000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>41000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-12000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-19000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>149000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>107000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-900000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-24000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>76000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>98000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>62000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-21000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-104000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-59000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-119000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-179000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-236000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>57000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2413,210 +2461,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-876000</v>
+        <v>-390000</v>
       </c>
       <c r="E26" s="3">
-        <v>-415000</v>
+        <v>-875000</v>
       </c>
       <c r="F26" s="3">
-        <v>432000</v>
+        <v>-419000</v>
       </c>
       <c r="G26" s="3">
-        <v>87000</v>
+        <v>433000</v>
       </c>
       <c r="H26" s="3">
+        <v>77000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-907000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-253000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>59000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-260000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-973000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-151000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>306000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>210000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>82000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>158000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>53000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>80000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-303000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-671000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-93000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>613000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>634000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-437000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-846000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-139000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>429000</v>
       </c>
-      <c r="G27" s="3">
-        <v>80000</v>
-      </c>
       <c r="H27" s="3">
-        <v>-873000</v>
+        <v>69000</v>
       </c>
       <c r="I27" s="3">
-        <v>-219000</v>
+        <v>-872000</v>
       </c>
       <c r="J27" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>56000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-232000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-955000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-159000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>292000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>207000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>77000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>150000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>140000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>69000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>109000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-314000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-689000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-105000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>530000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>580000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2716,8 +2773,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2769,8 +2829,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>11</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>11</v>
@@ -2787,11 +2847,11 @@
       <c r="Y29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>11</v>
@@ -2799,11 +2859,11 @@
       <c r="AC29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>11</v>
@@ -2817,8 +2877,11 @@
       <c r="AI29" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2918,8 +2981,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3019,210 +3085,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>8000</v>
+        <v>-47000</v>
       </c>
       <c r="E32" s="3">
-        <v>16000</v>
+        <v>-6000</v>
       </c>
       <c r="F32" s="3">
-        <v>-57000</v>
+        <v>-12000</v>
       </c>
       <c r="G32" s="3">
-        <v>33000</v>
+        <v>13000</v>
       </c>
       <c r="H32" s="3">
-        <v>29000</v>
+        <v>-40000</v>
       </c>
       <c r="I32" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L32" s="3">
         <v>23000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>73000</v>
+      </c>
+      <c r="P32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3">
-        <v>23000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>20000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>73000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>9000</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>34000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>51000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>27000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-17000</v>
       </c>
       <c r="U32" s="3">
         <v>-17000</v>
       </c>
       <c r="V32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-22000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>40000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>56000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>777000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-437000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-846000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-139000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>429000</v>
       </c>
-      <c r="G33" s="3">
-        <v>80000</v>
-      </c>
       <c r="H33" s="3">
-        <v>-873000</v>
+        <v>69000</v>
       </c>
       <c r="I33" s="3">
-        <v>-219000</v>
+        <v>-872000</v>
       </c>
       <c r="J33" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>56000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-232000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-955000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-159000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>292000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>207000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>77000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>150000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>140000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>69000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>109000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-314000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-689000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-105000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>530000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>580000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,215 +3397,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-437000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-846000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-139000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>429000</v>
       </c>
-      <c r="G35" s="3">
-        <v>80000</v>
-      </c>
       <c r="H35" s="3">
-        <v>-873000</v>
+        <v>69000</v>
       </c>
       <c r="I35" s="3">
-        <v>-219000</v>
+        <v>-872000</v>
       </c>
       <c r="J35" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>56000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-232000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-955000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-159000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>292000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>207000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>77000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>150000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>140000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>69000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>109000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-314000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-689000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-105000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>530000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>580000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3566,8 +3650,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3603,109 +3688,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3319000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2258000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2991000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3226000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2249000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2669000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2143000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2801000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2225000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2058000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2175000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2165000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2045000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2436000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1743000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2177000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1827000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2402000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1804000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1975000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1241000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2165000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1973000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1782000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>963000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>680000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>599000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>900000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>988000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3805,435 +3894,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3462000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3766000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3456000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3408000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3385000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3539000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3435000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3696000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3730000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4471000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4253000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4529000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4046000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4488000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4572000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4581000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4385000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4545000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5189000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5676000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5254000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5260000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5108000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5822000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3959000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3927000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3949000</v>
       </c>
-      <c r="F44" s="3">
-        <v>4022000</v>
-      </c>
       <c r="G44" s="3">
+        <v>4021000</v>
+      </c>
+      <c r="H44" s="3">
         <v>4051000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4109000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4118000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3833000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3859000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4049000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4012000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3818000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4167000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4362000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4406000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4403000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4516000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4361000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4290000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4422000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4636000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4850000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4782000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4731000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1681000</v>
+        <v>447000</v>
       </c>
       <c r="E45" s="3">
-        <v>1901000</v>
+        <v>585000</v>
       </c>
       <c r="F45" s="3">
-        <v>1830000</v>
+        <v>565000</v>
       </c>
       <c r="G45" s="3">
-        <v>1740000</v>
+        <v>574000</v>
       </c>
       <c r="H45" s="3">
-        <v>1771000</v>
+        <v>571000</v>
       </c>
       <c r="I45" s="3">
-        <v>1805000</v>
+        <v>542000</v>
       </c>
       <c r="J45" s="3">
+        <v>477000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1721000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1639000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1586000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2011000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2061000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1896000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1536000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1680000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1844000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1432000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1473000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1601000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1391000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1411000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1530000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1568000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12314000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11632000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12297000</v>
       </c>
-      <c r="F46" s="3">
-        <v>12486000</v>
-      </c>
       <c r="G46" s="3">
+        <v>12485000</v>
+      </c>
+      <c r="H46" s="3">
         <v>11425000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12088000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11501000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12051000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11453000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12164000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12451000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12573000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12154000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12822000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12401000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13005000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12160000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12781000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12884000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13464000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12542000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13805000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13431000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13794000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4310,210 +4414,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6036000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5931000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5982000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6147000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6028000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6130000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6171000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6158000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5990000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6181000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6396000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6477000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6547000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6658000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6641000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6855000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6709000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6611000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6710000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6950000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7111000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7232000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7302000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6868000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20880000</v>
+      </c>
+      <c r="E49" s="3">
         <v>21341000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22063000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22564000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22410000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22856000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23763000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23903000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24826000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25537000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27102000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>27506000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28011000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>28541000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>28747000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>29547000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>29536000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>34556000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>34746000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>36078000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>36535000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>37348000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>38013000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>38922000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4613,8 +4726,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4714,109 +4830,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2434000</v>
+        <v>458000</v>
       </c>
       <c r="E52" s="3">
-        <v>2431000</v>
+        <v>434000</v>
       </c>
       <c r="F52" s="3">
-        <v>2283000</v>
+        <v>471000</v>
       </c>
       <c r="G52" s="3">
-        <v>2225000</v>
+        <v>463000</v>
       </c>
       <c r="H52" s="3">
-        <v>2021000</v>
+        <v>477000</v>
       </c>
       <c r="I52" s="3">
-        <v>2021000</v>
+        <v>443000</v>
       </c>
       <c r="J52" s="3">
+        <v>449000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1899000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1983000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1110000</v>
       </c>
       <c r="N52" s="3">
         <v>1110000</v>
       </c>
       <c r="O52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="P52" s="3">
         <v>1139000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1174000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1215000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1233000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1332000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1043000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>990000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>978000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1058000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1108000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1099000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4916,109 +5038,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41758000</v>
+      </c>
+      <c r="E54" s="3">
         <v>41338000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42773000</v>
       </c>
-      <c r="F54" s="3">
-        <v>43480000</v>
-      </c>
       <c r="G54" s="3">
+        <v>43479000</v>
+      </c>
+      <c r="H54" s="3">
         <v>42088000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43095000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43456000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44011000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44252000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45932000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47059000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47666000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47851000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49195000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49004000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>50640000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49737000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>54991000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>55330000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>57470000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57246000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59424000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>59854000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>60683000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5054,8 +5182,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5091,614 +5220,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2371000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2366000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2439000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2602000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2280000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2508000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2381000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1887000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1635000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1901000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1750000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1686000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1514000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1551000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1692000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1756000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1716000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1606000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1710000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1718000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1688000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1806000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1763000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1853000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2580000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2094000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3060000</v>
       </c>
-      <c r="F58" s="3">
-        <v>1672000</v>
-      </c>
       <c r="G58" s="3">
+        <v>1769000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1479000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1980000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1023000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2109000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2769000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1719000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2077000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1426000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2709000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3530000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2697000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3188000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2106000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1649000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1630000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2345000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3130000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2771000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2790000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1700000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8577000</v>
+        <v>2864000</v>
       </c>
       <c r="E59" s="3">
-        <v>8293000</v>
+        <v>2939000</v>
       </c>
       <c r="F59" s="3">
-        <v>7973000</v>
+        <v>2822000</v>
       </c>
       <c r="G59" s="3">
-        <v>7635000</v>
+        <v>2351000</v>
       </c>
       <c r="H59" s="3">
-        <v>7355000</v>
+        <v>2361000</v>
       </c>
       <c r="I59" s="3">
-        <v>7007000</v>
+        <v>2341000</v>
       </c>
       <c r="J59" s="3">
+        <v>2374000</v>
+      </c>
+      <c r="K59" s="3">
         <v>7473000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7130000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7376000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7786000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7915000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7602000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7610000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7700000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8220000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8281000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8496000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8982000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9611000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9289000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9875000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9475000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10769000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13797000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13037000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13792000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12247000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11394000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11843000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10411000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11469000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11534000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10996000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11613000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11027000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11825000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12691000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12089000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13164000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12103000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11751000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12322000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13674000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14107000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14452000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14028000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14322000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16547000</v>
+        <v>16695000</v>
       </c>
       <c r="E61" s="3">
-        <v>16584000</v>
+        <v>16828000</v>
       </c>
       <c r="F61" s="3">
-        <v>18161000</v>
+        <v>16878000</v>
       </c>
       <c r="G61" s="3">
-        <v>18495000</v>
+        <v>18504000</v>
       </c>
       <c r="H61" s="3">
-        <v>18698000</v>
+        <v>18819000</v>
       </c>
       <c r="I61" s="3">
-        <v>19668000</v>
+        <v>19036000</v>
       </c>
       <c r="J61" s="3">
+        <v>20013000</v>
+      </c>
+      <c r="K61" s="3">
         <v>19103000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18497000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20363000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20840000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21617000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21037000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21602000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22288000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22731000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23515000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24616000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24473000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>24562000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>23812000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>25955000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25828000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>26691000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5191000</v>
+        <v>4344000</v>
       </c>
       <c r="E62" s="3">
-        <v>4854000</v>
+        <v>4357000</v>
       </c>
       <c r="F62" s="3">
-        <v>4945000</v>
+        <v>3991000</v>
       </c>
       <c r="G62" s="3">
-        <v>4687000</v>
+        <v>3996000</v>
       </c>
       <c r="H62" s="3">
-        <v>4846000</v>
+        <v>3820000</v>
       </c>
       <c r="I62" s="3">
-        <v>4765000</v>
+        <v>3974000</v>
       </c>
       <c r="J62" s="3">
+        <v>3871000</v>
+      </c>
+      <c r="K62" s="3">
         <v>4841000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4702000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4745000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4346000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3778000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3538000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3591000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3652000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3684000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3527000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3800000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3947000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4171000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4402000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3766000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4177000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3876000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5798,8 +5946,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5899,8 +6050,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6000,109 +6154,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>34979000</v>
+        <v>35374000</v>
       </c>
       <c r="E66" s="3">
-        <v>35495000</v>
+        <v>34775000</v>
       </c>
       <c r="F66" s="3">
-        <v>35973000</v>
+        <v>35230000</v>
       </c>
       <c r="G66" s="3">
-        <v>35158000</v>
+        <v>35353000</v>
       </c>
       <c r="H66" s="3">
-        <v>36043000</v>
+        <v>34577000</v>
       </c>
       <c r="I66" s="3">
-        <v>35595000</v>
+        <v>35387000</v>
       </c>
       <c r="J66" s="3">
+        <v>34845000</v>
+      </c>
+      <c r="K66" s="3">
         <v>36207000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35484000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36895000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37715000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37388000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37384000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38871000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39004000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40614000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40144000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>41139000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41799000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43498000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>43455000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45301000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45122000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45976000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6138,8 +6298,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6239,8 +6400,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6340,8 +6504,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6415,19 +6582,19 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AF70" s="3">
         <v>3620000</v>
@@ -6441,8 +6608,11 @@
       <c r="AI70" s="3">
         <v>3620000</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>3620000</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6542,109 +6712,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14956000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14519000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6744,8 +6920,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6845,8 +7024,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6946,109 +7128,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6065000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6359000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7278000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7506000</v>
       </c>
-      <c r="G76" s="3">
-        <v>6930000</v>
-      </c>
       <c r="H76" s="3">
+        <v>6929000</v>
+      </c>
+      <c r="I76" s="3">
         <v>7052000</v>
       </c>
-      <c r="I76" s="3">
-        <v>7861000</v>
-      </c>
       <c r="J76" s="3">
+        <v>7860000</v>
+      </c>
+      <c r="K76" s="3">
         <v>7804000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8768000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9037000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9344000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10278000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10467000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10324000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10000000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10026000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9593000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13852000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13531000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13972000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13791000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14123000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14732000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14707000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7148,215 +7336,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-437000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-846000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-139000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>429000</v>
       </c>
-      <c r="G81" s="3">
-        <v>80000</v>
-      </c>
       <c r="H81" s="3">
-        <v>-873000</v>
+        <v>69000</v>
       </c>
       <c r="I81" s="3">
-        <v>-219000</v>
+        <v>-872000</v>
       </c>
       <c r="J81" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>56000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-232000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-955000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-159000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>292000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>207000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>77000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>150000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>140000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>69000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>109000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-314000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-689000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-105000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>530000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>580000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7392,109 +7589,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>259000</v>
+        <v>138000</v>
       </c>
       <c r="E83" s="3">
-        <v>272000</v>
+        <v>138000</v>
       </c>
       <c r="F83" s="3">
-        <v>266000</v>
+        <v>139000</v>
       </c>
       <c r="G83" s="3">
-        <v>283000</v>
+        <v>150000</v>
       </c>
       <c r="H83" s="3">
-        <v>300000</v>
+        <v>156000</v>
       </c>
       <c r="I83" s="3">
-        <v>304000</v>
+        <v>146000</v>
       </c>
       <c r="J83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="K83" s="3">
         <v>306000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>321000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>358000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>323000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>320000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>329000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>305000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>376000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>395000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>381000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>382000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>399000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>416000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>413000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>450000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>443000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>382000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>474000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>479000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>507000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>528000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>527000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>577000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>480000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>332000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7594,8 +7795,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7695,8 +7899,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7796,8 +8003,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7897,8 +8107,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7998,109 +8211,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>104000</v>
+        <v>693000</v>
       </c>
       <c r="E89" s="3">
-        <v>-125000</v>
+        <v>103000</v>
       </c>
       <c r="F89" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="G89" s="3">
         <v>1184000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>324000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-145000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>973000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>544000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>122000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-49000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>456000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>529000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>218000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-405000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>331000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>307000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>273000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>305000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>538000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>325000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-227000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>112000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>367000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>421000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>162000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>741000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>470000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8136,109 +8355,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-97000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-124000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-119000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-149000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-119000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-139000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-142000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-122000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-127000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-157000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-153000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-146000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-113000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-150000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-176000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-143000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-131000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-128000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-119000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-169000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-112000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-125000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8338,8 +8561,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8439,109 +8665,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E94" s="3">
         <v>178000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>144000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>301000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>184000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>302000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>181000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>168000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>147000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>180000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>161000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>246000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>288000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>481000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>508000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>141000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>157000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>313000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>252000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>430000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>224000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>429000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>272000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>74000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>347000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>406000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>744000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8577,31 +8809,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8658,28 +8891,31 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AH96" s="3">
         <v>-346000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8779,8 +9015,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8880,8 +9119,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8981,307 +9223,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="3">
         <v>-966000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-576000</v>
       </c>
       <c r="G100" s="3">
         <v>-576000</v>
       </c>
       <c r="H100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-55000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-706000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-711000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-440000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-338000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-501000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-493000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-125000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-700000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-241000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-189000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>146000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>146000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>25000</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-49000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-104000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>68000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-33000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>12000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>146000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-84000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-123000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-62000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-48000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="AC101" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>18000</v>
       </c>
-      <c r="T101" s="3">
-        <v>15000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="AF101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>25000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-35000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-49000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-69000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>18000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>7000</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>28000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-733000</v>
+        <v>1061000</v>
       </c>
       <c r="E102" s="3">
-        <v>-236000</v>
+        <v>-734000</v>
       </c>
       <c r="F102" s="3">
+        <v>-235000</v>
+      </c>
+      <c r="G102" s="3">
         <v>977000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-420000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>494000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-658000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>576000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>167000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-159000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>52000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>153000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-391000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>693000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-434000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>350000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-575000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>598000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-171000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>734000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-924000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>192000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>191000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>443000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>455000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>283000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>81000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,457 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4229000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4332000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4164000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3819000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4457000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3850000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3878000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3661000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3884000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3595000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3786000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3661000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4100000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3887000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3910000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3982000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4453000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3978000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3870000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4357000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3991000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4093000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4177000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4149000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4559000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2183000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2140000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2048000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2041000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1999000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2082000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2079000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1784000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1885000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1958000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1859000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1975000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1987000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2063000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2372000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2128000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2091000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2279000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2033000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>2258000</v>
       </c>
       <c r="Z9" s="3">
         <v>2258000</v>
       </c>
       <c r="AA9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="AB9" s="3">
         <v>2693000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2120000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2149000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2024000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1771000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2416000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1851000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1796000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1582000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2100000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1710000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1828000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1802000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2125000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1898000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1923000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1919000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2081000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1850000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1779000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2078000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1958000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1864000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1919000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1891000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1866000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1143,112 +1155,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E12" s="3">
         <v>240000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>269000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>242000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>227000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>253000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>240000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>234000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>210000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>175000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>228000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>225000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>249000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>222000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>243000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>254000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>296000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>238000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>242000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>221000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>232000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>487000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>276000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>261000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>295000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>311000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>290000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>317000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>346000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>531000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>469000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>432000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>684000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1351,177 +1367,183 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>922000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1053000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>823000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>877000</v>
       </c>
-      <c r="G14" s="3">
-        <v>529000</v>
-      </c>
       <c r="H14" s="3">
+        <v>495000</v>
+      </c>
+      <c r="I14" s="3">
         <v>416000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1324000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>512000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1978000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>321000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1683000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1502000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>893000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>183000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>247000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>360000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>374000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5077000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>516000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>764000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>561000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>832000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1323000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>561000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3804000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>855000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>520000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>205000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>259000</v>
+        <v>269000</v>
       </c>
       <c r="E15" s="3">
         <v>259000</v>
       </c>
       <c r="F15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="G15" s="3">
         <v>272000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>266000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>283000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>300000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>304000</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>25000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>27000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>31000</v>
       </c>
       <c r="T15" s="3">
         <v>31000</v>
       </c>
       <c r="U15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="V15" s="3">
         <v>30000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>35000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>34000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>35000</v>
       </c>
       <c r="Y15" s="3">
         <v>35000</v>
@@ -1530,28 +1552,28 @@
         <v>35000</v>
       </c>
       <c r="AA15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>24000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>51000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>41000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>46000</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
-      </c>
       <c r="AF15" s="3">
         <v>0</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>11</v>
+      <c r="AH15" s="3">
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>11</v>
@@ -1559,8 +1581,11 @@
       <c r="AJ15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1594,216 +1619,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3336000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3328000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3347000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3159000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3207000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3206000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3089000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3208000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3162000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4837000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3176000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4735000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4374000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4022000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3264000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3328000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3548000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4048000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8320000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3697000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4166000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3843000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4174000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4821000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4015000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7709000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>893000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1004000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>817000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>660000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1250000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1251000</v>
+      </c>
+      <c r="I18" s="3">
         <v>761000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>670000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>499000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-953000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>419000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-949000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-713000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>78000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>623000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>582000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>434000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>405000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>173000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>191000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>148000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-81000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-644000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>134000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>378000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>895000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1840,266 +1872,273 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E20" s="3">
         <v>47000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-13000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I20" s="3">
         <v>40000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>43000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-23000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-73000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-34000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-51000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-27000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>124000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>17000</v>
       </c>
       <c r="V20" s="3">
         <v>17000</v>
       </c>
       <c r="W20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="X20" s="3">
         <v>22000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>14000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>30000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>290000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1177000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1216000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1070000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>920000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1529000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1004000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>927000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>805000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-656000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>717000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-577000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-410000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>325000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>943000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>853000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>759000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>773000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>572000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>607000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>586000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>340000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-174000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>586000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>501000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>460000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>865000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E22" s="3">
         <v>225000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>233000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>242000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>328000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>240000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>226000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>261000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>237000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>230000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>225000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>238000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>180000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>232000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>240000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>239000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>241000</v>
       </c>
       <c r="T22" s="3">
         <v>241000</v>
@@ -2111,257 +2150,266 @@
         <v>241000</v>
       </c>
       <c r="W22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="X22" s="3">
         <v>209000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>219000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>226000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>227000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>231000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>240000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>231000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>218000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>221000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>219000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>526000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AI22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-247000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-321000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-245000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-471000</v>
       </c>
-      <c r="G23" s="3">
-        <v>474000</v>
-      </c>
       <c r="H23" s="3">
+        <v>508000</v>
+      </c>
+      <c r="I23" s="3">
         <v>65000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-923000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-272000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>166000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-971000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-175000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>382000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>308000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>144000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>137000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-51000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-33000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-39000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-292000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-850000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-213000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>119000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>688000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E24" s="3">
         <v>69000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>630000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-52000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>41000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-19000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>149000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>107000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-900000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-24000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>76000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>98000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>62000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-104000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-59000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-119000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-179000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-236000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>57000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2464,216 +2512,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-390000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-875000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-419000</v>
       </c>
-      <c r="G26" s="3">
-        <v>433000</v>
-      </c>
       <c r="H26" s="3">
+        <v>467000</v>
+      </c>
+      <c r="I26" s="3">
         <v>77000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-907000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-253000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>59000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-260000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-973000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-151000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>306000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>210000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>82000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>158000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>53000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>80000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-303000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-671000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-93000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>613000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>634000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-437000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-846000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-139000</v>
       </c>
-      <c r="G27" s="3">
-        <v>429000</v>
-      </c>
       <c r="H27" s="3">
+        <v>463000</v>
+      </c>
+      <c r="I27" s="3">
         <v>69000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-872000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-220000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>56000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-232000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-955000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-159000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>292000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>207000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>77000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>150000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>140000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>69000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>109000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-314000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-689000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-105000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>530000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>580000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2776,8 +2833,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2832,8 +2892,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>11</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>11</v>
@@ -2850,11 +2910,11 @@
       <c r="Z29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>11</v>
@@ -2862,11 +2922,11 @@
       <c r="AD29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>11</v>
@@ -2880,8 +2940,11 @@
       <c r="AJ29" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2984,8 +3047,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3088,216 +3154,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-47000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12000</v>
       </c>
-      <c r="G32" s="3">
-        <v>13000</v>
-      </c>
       <c r="H32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-40000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-43000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>23000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>73000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>34000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>51000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>27000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-17000</v>
       </c>
       <c r="V32" s="3">
         <v>-17000</v>
       </c>
       <c r="W32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="X32" s="3">
         <v>-22000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>40000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>56000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>777000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-437000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-846000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-139000</v>
       </c>
-      <c r="G33" s="3">
-        <v>429000</v>
-      </c>
       <c r="H33" s="3">
+        <v>463000</v>
+      </c>
+      <c r="I33" s="3">
         <v>69000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-872000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-220000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>56000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-232000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-955000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-159000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>292000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>207000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>77000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>150000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>140000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>69000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>109000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-314000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-689000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-105000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>530000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>580000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3400,221 +3475,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-437000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-846000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-139000</v>
       </c>
-      <c r="G35" s="3">
-        <v>429000</v>
-      </c>
       <c r="H35" s="3">
+        <v>463000</v>
+      </c>
+      <c r="I35" s="3">
         <v>69000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-872000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-220000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>56000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-232000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-955000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-159000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>292000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>207000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>77000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>150000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>140000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>69000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>109000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-314000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-689000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-105000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>530000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>580000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3651,8 +3735,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3689,112 +3774,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3319000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2258000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2991000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3226000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2249000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2669000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2143000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2801000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2225000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2058000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2175000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2165000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2045000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2436000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1743000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2177000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1827000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2402000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1804000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1975000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1241000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2165000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1973000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1782000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>963000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>680000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>599000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>900000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>988000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3897,424 +3986,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3059000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3462000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3766000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3456000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3408000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3385000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3539000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3435000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3696000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3730000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4471000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4253000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4529000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4046000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4488000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4572000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4581000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4385000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4545000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5189000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5676000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5254000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5260000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5108000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5822000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3007000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3959000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3927000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3949000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4021000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4051000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4109000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4118000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3833000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3859000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4049000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4012000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3818000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4167000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4362000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4406000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4403000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4516000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4361000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4290000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4422000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4636000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4850000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4782000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4731000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2180000</v>
+      </c>
+      <c r="E45" s="3">
         <v>447000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>585000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>565000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>574000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>571000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>542000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>477000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1721000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1639000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1586000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2011000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2061000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1896000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1536000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1680000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1844000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1432000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1473000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1601000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1391000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1411000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1530000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1568000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12552000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12314000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11632000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12297000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12485000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11425000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12088000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11501000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12051000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11453000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12164000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12451000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12573000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12154000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12822000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12401000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13005000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12160000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12781000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12884000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13464000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12542000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13805000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13431000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13794000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4327,11 +4431,11 @@
       <c r="F47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="3">
         <v>8000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>11</v>
@@ -4339,8 +4443,8 @@
       <c r="J47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4417,216 +4521,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4948000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6036000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5931000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5982000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6147000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6028000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6130000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6171000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6158000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5990000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6181000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6396000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6477000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6547000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6658000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6641000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6855000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6709000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6611000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6710000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6950000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7111000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7232000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7302000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6868000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19565000</v>
+      </c>
+      <c r="E49" s="3">
         <v>20880000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21341000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22063000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22564000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22410000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22856000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23763000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23903000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24826000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>25537000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>27102000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27506000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>28011000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>28541000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>28747000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>29547000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>29536000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>34556000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34746000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>36078000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>36535000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>37348000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>38013000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>38922000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4729,8 +4842,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4833,112 +4949,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E52" s="3">
         <v>458000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>434000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>471000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>463000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>477000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>443000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>449000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1899000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1983000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1110000</v>
       </c>
       <c r="O52" s="3">
         <v>1110000</v>
       </c>
       <c r="P52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1139000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1174000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1215000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1233000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1332000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1043000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>990000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>978000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1058000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1039000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1099000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5041,112 +5163,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39326000</v>
+      </c>
+      <c r="E54" s="3">
         <v>41758000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>41338000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42773000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43479000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42088000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43095000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43456000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44011000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44252000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>45932000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47059000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47666000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47851000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49195000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>49004000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>50640000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49737000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>54991000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55330000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57470000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>57246000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>59424000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59854000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60683000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5183,8 +5311,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5221,632 +5350,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2203000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2371000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2366000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2439000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2602000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2280000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2508000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2381000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1887000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1635000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1901000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1750000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1686000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1514000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1551000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1692000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1756000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1716000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1606000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1710000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1718000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1688000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1806000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1763000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1853000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1868000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2580000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2094000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3060000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1769000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1479000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1980000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1023000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2109000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2769000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1719000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2077000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1426000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2709000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3530000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2697000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3188000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2106000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1649000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1630000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2345000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3130000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2771000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2790000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1700000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3074000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2864000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2939000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2822000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2351000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2361000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2341000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2374000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7473000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7130000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7376000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7786000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7915000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7602000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7610000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7700000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8220000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8281000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8496000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8982000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9611000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9289000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9875000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9475000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10769000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12796000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13797000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13037000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13792000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12247000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11394000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11843000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10411000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11469000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11534000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10996000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11613000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11027000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11825000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12691000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12089000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13164000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12103000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11751000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12322000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13674000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14107000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14452000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14028000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14322000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16316000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16695000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16828000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16878000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18504000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18819000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19036000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20013000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19103000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18497000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20363000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20840000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21617000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21037000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21602000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22288000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22731000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23515000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24616000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>24473000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24562000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>23812000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25955000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>25828000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26691000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3948000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4344000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4357000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3991000</v>
       </c>
-      <c r="G62" s="3">
-        <v>3996000</v>
-      </c>
       <c r="H62" s="3">
+        <v>3923000</v>
+      </c>
+      <c r="I62" s="3">
         <v>3820000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3974000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3871000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4841000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4702000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4745000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4346000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3778000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3538000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3591000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3652000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3684000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3527000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3800000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3947000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4171000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4402000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3766000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4177000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3876000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5949,8 +6097,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6053,8 +6204,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6157,112 +6311,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33606000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35374000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34775000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35230000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35353000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34577000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35387000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34845000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36207000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35484000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36895000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37715000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37388000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37384000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38871000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39004000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40614000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40144000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41139000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>41799000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>43498000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>43455000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45301000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45122000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45976000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6299,8 +6459,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6403,8 +6564,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6507,8 +6671,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6585,19 +6752,19 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AG70" s="3">
         <v>3620000</v>
@@ -6611,8 +6778,11 @@
       <c r="AJ70" s="3">
         <v>3620000</v>
       </c>
+      <c r="AK70" s="3">
+        <v>3620000</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6715,112 +6885,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15173000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14956000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14519000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6923,8 +7099,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7027,8 +7206,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7131,112 +7313,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5373000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6065000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6359000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7278000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7506000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6929000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7052000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7860000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7804000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8768000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9037000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9344000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10278000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10467000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10324000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10000000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10026000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9593000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13852000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13531000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13972000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13791000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14123000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14732000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14707000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7339,221 +7527,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-437000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-846000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-139000</v>
       </c>
-      <c r="G81" s="3">
-        <v>429000</v>
-      </c>
       <c r="H81" s="3">
+        <v>463000</v>
+      </c>
+      <c r="I81" s="3">
         <v>69000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-872000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-220000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>56000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-232000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-955000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-159000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>292000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>207000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>77000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>150000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>140000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>69000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>109000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-314000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-689000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-105000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>530000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>580000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7590,112 +7787,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>138000</v>
+        <v>121000</v>
       </c>
       <c r="E83" s="3">
         <v>138000</v>
       </c>
       <c r="F83" s="3">
+        <v>138000</v>
+      </c>
+      <c r="G83" s="3">
         <v>139000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>150000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>156000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>146000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>123000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>306000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>321000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>358000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>323000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>320000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>329000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>305000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>376000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>395000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>381000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>382000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>399000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>416000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>413000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>450000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>443000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>382000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>474000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>479000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>507000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>528000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>527000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>577000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>480000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>332000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7798,8 +7999,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7902,8 +8106,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8006,8 +8213,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8110,8 +8320,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8214,112 +8427,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E89" s="3">
         <v>693000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>103000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-124000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1184000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>324000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-145000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>973000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>544000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>122000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-49000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>456000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>529000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>218000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-405000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>331000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>307000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>273000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>305000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>538000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>325000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-227000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>112000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>367000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>421000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>162000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>741000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>470000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8356,112 +8575,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-148000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-97000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-124000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-119000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-149000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-119000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-139000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-142000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-122000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-127000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-157000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-153000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-146000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-113000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-150000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-176000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-143000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-131000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-128000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-119000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-169000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-112000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8564,8 +8787,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8668,112 +8894,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E94" s="3">
         <v>268000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>178000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>144000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>301000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>184000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>302000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>181000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>168000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>147000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>180000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>161000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>246000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>288000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>481000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>508000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>141000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>157000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>313000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>252000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>430000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>224000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>429000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>272000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>74000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>347000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>406000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>744000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8810,8 +9042,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8836,8 +9069,8 @@
       <c r="J96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8894,28 +9127,31 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AI96" s="3">
         <v>-346000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9018,8 +9254,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9122,8 +9361,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9226,316 +9468,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>-674000</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-966000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-576000</v>
       </c>
       <c r="H100" s="3">
         <v>-576000</v>
       </c>
       <c r="I100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-55000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-706000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-711000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-440000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-338000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-501000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-493000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-125000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-700000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-241000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-189000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-33000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-77000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>146000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-84000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-123000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-62000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>146000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-84000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-123000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-62000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-48000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-44000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>18000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>15000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-28000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>25000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>11000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>18000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>28000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1061000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-734000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-235000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>977000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-420000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>494000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-658000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>576000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>167000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-159000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>52000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>153000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>693000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-434000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>350000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-575000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>598000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-171000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>734000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-924000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>192000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>191000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>443000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>455000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>283000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>81000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,469 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3891000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4229000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4332000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4164000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3819000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4457000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3850000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3878000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3661000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3884000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3595000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3786000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3661000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4100000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3887000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3910000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3982000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4453000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3978000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3870000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4357000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3991000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4093000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4177000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4149000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4559000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2014000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2109000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2183000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2140000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2048000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2041000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1999000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2082000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2079000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1784000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1885000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1958000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1859000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1975000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1989000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1987000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2063000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2372000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2128000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2091000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2279000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2033000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>2258000</v>
       </c>
       <c r="AA9" s="3">
         <v>2258000</v>
       </c>
       <c r="AB9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="AC9" s="3">
         <v>2693000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2120000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2149000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2024000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1771000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2416000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1851000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1796000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1582000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2100000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1710000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1828000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1802000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2125000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1898000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1923000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1919000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2081000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1850000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1779000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2078000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1958000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1864000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1919000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1891000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1866000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1156,8 +1168,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,106 +1178,109 @@
         <v>247000</v>
       </c>
       <c r="E12" s="3">
+        <v>247000</v>
+      </c>
+      <c r="F12" s="3">
         <v>240000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>269000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>242000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>227000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>253000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>240000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>234000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>210000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>175000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>228000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>225000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>249000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>222000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>243000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>254000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>296000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>238000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>242000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>221000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>232000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>487000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>276000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>261000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>295000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>311000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>290000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>317000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>346000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>531000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>469000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>432000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>684000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1370,183 +1386,189 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E14" s="3">
         <v>922000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1053000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>823000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>877000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>495000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>416000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1324000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>512000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1978000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>321000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1683000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1502000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>893000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>183000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>247000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>360000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>374000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5077000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>516000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>764000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>561000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>832000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1323000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>561000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3804000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>855000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>520000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>205000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E15" s="3">
         <v>269000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>259000</v>
       </c>
       <c r="F15" s="3">
         <v>259000</v>
       </c>
       <c r="G15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="H15" s="3">
         <v>272000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>266000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>283000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>304000</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>24000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>25000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>27000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>31000</v>
       </c>
       <c r="U15" s="3">
         <v>31000</v>
       </c>
       <c r="V15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="W15" s="3">
         <v>30000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>35000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>34000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>35000</v>
       </c>
       <c r="Z15" s="3">
         <v>35000</v>
@@ -1555,28 +1577,28 @@
         <v>35000</v>
       </c>
       <c r="AB15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>24000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>51000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>41000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>46000</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
-      </c>
       <c r="AG15" s="3">
         <v>0</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>11</v>
+      <c r="AI15" s="3">
+        <v>0</v>
       </c>
       <c r="AJ15" s="3" t="s">
         <v>11</v>
@@ -1584,8 +1606,11 @@
       <c r="AK15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1620,222 +1645,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3182000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3336000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3328000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3347000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3159000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3206000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3089000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3208000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3162000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4837000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3176000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4735000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4374000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4022000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3264000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3328000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3548000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4048000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8320000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3697000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4166000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3843000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4174000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4821000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4015000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7709000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>709000</v>
+      </c>
+      <c r="E18" s="3">
         <v>893000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1004000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>817000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>660000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1251000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>761000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>670000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>499000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-953000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>419000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-949000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-713000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>78000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>623000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>582000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>434000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>405000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>173000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>191000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>148000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-81000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-644000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>134000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>16000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>378000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>895000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1873,275 +1905,282 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>47000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
-        <v>12000</v>
-      </c>
       <c r="H20" s="3">
+        <v>29000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>40000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>43000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-23000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-20000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-34000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-51000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-27000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>124000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>17000</v>
       </c>
       <c r="W20" s="3">
         <v>17000</v>
       </c>
       <c r="X20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>22000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>11000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>30000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>290000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>938000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1177000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1216000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1070000</v>
       </c>
-      <c r="G21" s="3">
-        <v>920000</v>
-      </c>
       <c r="H21" s="3">
+        <v>903000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1529000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1004000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>927000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>805000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-656000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>717000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-577000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-410000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>325000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>943000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>853000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>759000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>773000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>572000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>607000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>586000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>340000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-174000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>586000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>501000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>460000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>865000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E22" s="3">
         <v>319000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>225000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>233000</v>
       </c>
-      <c r="G22" s="3">
-        <v>242000</v>
-      </c>
       <c r="H22" s="3">
+        <v>225000</v>
+      </c>
+      <c r="I22" s="3">
         <v>328000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>240000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>226000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>261000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>237000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>230000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>225000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>238000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>180000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>232000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>240000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>239000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>241000</v>
       </c>
       <c r="U22" s="3">
         <v>241000</v>
@@ -2153,263 +2192,272 @@
         <v>241000</v>
       </c>
       <c r="X22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>209000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>219000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>226000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>227000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>231000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>240000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>231000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>218000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>221000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>219000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>526000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AJ22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AK22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL22" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>294000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-247000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-321000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-245000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-471000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>508000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>65000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-923000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-272000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>166000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-971000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-175000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>382000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>308000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>144000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>137000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-51000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-33000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-292000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-850000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-213000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>119000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>688000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E24" s="3">
         <v>28000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>69000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>630000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-52000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>41000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-12000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-19000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>149000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>107000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-900000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>76000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>98000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>62000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-21000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-104000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-59000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-119000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-179000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-236000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>46000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>54000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>57000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2515,222 +2563,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-275000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-390000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-875000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-419000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>467000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>77000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-907000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-253000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>59000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-260000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-973000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-151000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>306000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>210000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>82000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>158000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>53000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>80000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-303000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-671000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-93000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>613000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>634000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-217000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-437000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-846000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-139000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>463000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>69000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-872000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-220000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>56000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-232000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-955000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>292000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>207000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>77000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>150000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>140000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>69000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>109000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-314000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-689000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-105000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>530000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>580000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2836,8 +2893,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2895,8 +2955,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>11</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>11</v>
@@ -2913,11 +2973,11 @@
       <c r="AA29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>11</v>
@@ -2925,11 +2985,11 @@
       <c r="AE29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>11</v>
@@ -2943,8 +3003,11 @@
       <c r="AK29" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3050,8 +3113,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3157,222 +3223,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E32" s="3">
         <v>15000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-47000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-12000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="I32" s="3">
         <v>12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-40000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-43000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>23000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>20000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>73000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>34000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>51000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>27000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-17000</v>
       </c>
       <c r="W32" s="3">
         <v>-17000</v>
       </c>
       <c r="X32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>40000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>56000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>777000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-217000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-437000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-846000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-139000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>463000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>69000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-872000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-220000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>56000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-232000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-955000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>292000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>207000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>77000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>150000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>140000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>69000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>109000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-314000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-689000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-105000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>530000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>580000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3478,227 +3553,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-217000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-437000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-846000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-139000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>463000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>69000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-872000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-220000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>56000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-232000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-955000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>292000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>207000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>77000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>150000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>140000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>69000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>109000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-314000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-689000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-105000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>530000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>580000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3736,8 +3820,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3775,115 +3860,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1697000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3300000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3319000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2258000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2991000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3226000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2249000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2669000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2143000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2801000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2225000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2058000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2175000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2165000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2045000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2436000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1743000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2177000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1827000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2402000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1804000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1975000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1241000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2165000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1973000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1782000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>963000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>680000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>599000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>900000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>988000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3989,436 +4078,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3384000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3059000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3462000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3766000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3456000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3408000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3385000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3539000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3435000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3696000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3730000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4471000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4253000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4529000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4046000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4488000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4572000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4581000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4385000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4545000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5189000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5676000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5254000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5260000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5108000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5822000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3247000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3007000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3959000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3927000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3949000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4021000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4051000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4109000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4118000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3833000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3859000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4049000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4012000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3818000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4167000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4362000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4406000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4403000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4516000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4361000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4290000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4422000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4636000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4850000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4782000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4731000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2182000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2180000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>447000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>585000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>565000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>574000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>571000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>542000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>477000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1721000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1639000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1586000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2011000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2061000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1896000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1536000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1680000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1844000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1432000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1473000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1601000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1391000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1411000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1530000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1568000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11528000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12552000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12314000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11632000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12297000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12485000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11425000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12088000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11501000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12051000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11453000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12164000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12451000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12573000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12154000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12822000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12401000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13005000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12160000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12781000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12884000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13464000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12542000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13805000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13431000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13794000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4434,11 +4538,11 @@
       <c r="G47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="3">
         <v>8000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>11</v>
@@ -4446,8 +4550,8 @@
       <c r="K47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4524,222 +4628,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4994000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4948000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6036000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5931000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5982000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6147000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6028000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6130000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6171000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6158000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5990000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6181000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6396000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6477000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6547000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6658000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6641000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6855000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6709000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6611000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6710000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6950000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7111000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7232000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7302000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6868000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19666000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19565000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20880000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21341000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22063000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22564000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22410000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22856000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23763000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23903000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>24826000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>25537000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27102000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27506000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>28011000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>28541000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>28747000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>29547000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>29536000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34556000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34746000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>36078000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>36535000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>37348000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>38013000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>38922000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4845,8 +4958,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4952,115 +5068,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E52" s="3">
         <v>462000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>458000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>434000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>471000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>463000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>477000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>443000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>449000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1899000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1983000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1110000</v>
       </c>
       <c r="P52" s="3">
         <v>1110000</v>
       </c>
       <c r="Q52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="R52" s="3">
         <v>1139000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1174000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1215000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1233000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1332000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1043000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>990000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>978000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1058000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1039000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1099000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5166,115 +5288,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>38415000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39326000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>41758000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41338000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42773000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43479000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42088000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43095000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43456000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44011000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44252000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45932000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47059000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47666000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47851000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>49195000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49004000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>50640000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49737000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>54991000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>55330000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>57470000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>57246000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59424000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59854000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60683000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5312,8 +5440,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5351,650 +5480,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2290000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2203000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2371000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2366000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2439000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2602000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2280000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2508000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2381000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1887000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1635000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1901000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1750000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1686000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1514000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1551000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1692000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1756000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1716000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1606000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1710000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1718000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1688000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1806000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1763000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1853000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1868000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2580000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2094000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3060000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1769000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1479000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1980000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1023000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2109000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2769000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1719000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2077000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1426000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2709000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3530000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2697000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3188000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2106000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1649000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1630000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2345000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3130000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2771000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2790000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1700000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2737000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3074000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2864000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2939000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2822000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2351000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2361000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2341000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2374000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7473000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7130000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7376000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7786000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7915000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7602000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7610000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7700000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8220000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8281000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8496000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8982000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9611000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9289000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9875000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9475000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10769000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11157000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12796000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13797000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13037000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13792000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12247000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11394000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11843000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10411000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11469000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11534000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10996000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11613000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11027000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11825000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12691000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12089000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13164000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12103000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11751000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12322000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13674000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14107000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14452000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14028000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14322000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16518000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16316000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16695000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16828000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16878000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18504000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18819000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19036000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20013000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19103000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18497000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20363000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20840000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21617000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21037000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21602000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22288000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>22731000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23515000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>24616000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24473000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>24562000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>23812000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>25955000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25828000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26691000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4010000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3948000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4344000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4357000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3991000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3923000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3820000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3974000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3871000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4841000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4702000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4745000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4346000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3778000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3538000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3591000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3652000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3684000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3527000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3800000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3947000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4171000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4402000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3766000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4177000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3876000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6100,8 +6248,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6207,8 +6358,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6314,115 +6468,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32146000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33606000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35374000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34775000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35230000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35353000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34577000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35387000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34845000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36207000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35484000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36895000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37715000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37388000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37384000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38871000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39004000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40614000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>40144000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>41139000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>41799000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>43498000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>43455000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45301000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45122000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>45976000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6460,8 +6620,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6567,8 +6728,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6674,8 +6838,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6755,19 +6922,19 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AG70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AH70" s="3">
         <v>3620000</v>
@@ -6781,8 +6948,11 @@
       <c r="AK70" s="3">
         <v>3620000</v>
       </c>
+      <c r="AL70" s="3">
+        <v>3620000</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6888,115 +7058,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14958000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15173000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14956000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14519000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7102,8 +7278,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7209,8 +7388,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7316,115 +7498,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6262000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5373000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6065000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6359000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7278000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7506000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6929000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7052000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7860000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7804000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8768000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9037000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9344000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10278000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10467000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10324000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10000000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10026000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9593000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13852000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13531000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13972000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13791000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14123000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14732000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14707000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7530,227 +7718,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-217000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-437000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-846000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-139000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>463000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>69000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-872000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-220000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>56000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-232000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-955000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>292000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>207000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>77000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>150000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>140000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>69000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>109000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-314000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-689000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-105000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>530000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>580000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7788,115 +7985,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E83" s="3">
         <v>121000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>138000</v>
       </c>
       <c r="F83" s="3">
         <v>138000</v>
       </c>
       <c r="G83" s="3">
+        <v>138000</v>
+      </c>
+      <c r="H83" s="3">
         <v>139000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>150000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>156000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>146000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>123000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>306000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>321000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>358000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>323000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>320000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>329000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>305000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>376000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>395000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>381000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>382000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>399000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>416000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>413000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>450000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>443000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>382000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>474000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>479000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>507000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>528000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>527000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>577000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>480000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>332000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8002,8 +8203,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8109,8 +8313,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8216,8 +8423,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8323,8 +8533,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8430,115 +8643,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E89" s="3">
         <v>575000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>693000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>103000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-124000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1184000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>324000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-145000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>973000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>544000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>122000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-49000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>456000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>529000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>218000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-405000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>331000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>307000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>273000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>305000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>538000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>325000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-227000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>112000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>367000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>421000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>162000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>741000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>470000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8576,115 +8795,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-129000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-148000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-97000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-124000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-119000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-149000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-119000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-139000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-142000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-122000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-127000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-157000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-153000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-146000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-113000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-150000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-176000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-143000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-128000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-119000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-169000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8790,8 +9013,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8897,115 +9123,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E94" s="3">
         <v>202000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>268000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>178000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>144000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>301000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>184000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>302000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>181000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>168000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>147000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>180000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>161000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>246000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>288000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>481000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>508000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>141000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>157000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>313000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>252000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>430000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>224000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>429000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>272000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>74000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>347000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>406000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>744000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9043,8 +9275,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9072,8 +9305,8 @@
       <c r="K96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9130,28 +9363,31 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-346000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9257,8 +9493,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9364,8 +9603,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9471,325 +9713,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1744000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-674000</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-966000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-576000</v>
       </c>
       <c r="I100" s="3">
         <v>-576000</v>
       </c>
       <c r="J100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-55000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-706000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-711000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-440000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-338000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-501000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-493000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-125000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-700000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-241000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-189000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E101" s="3">
         <v>68000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-33000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-77000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>146000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-84000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-123000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-62000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>146000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-84000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-123000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-62000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-31000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-44000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>18000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>15000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-28000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>25000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>18000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>7000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1603000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1061000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-734000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-235000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>977000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-420000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>494000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-658000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>576000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>167000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-159000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>153000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-391000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>693000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-434000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>350000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-575000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>598000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-171000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>734000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-924000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>192000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>191000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>443000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>455000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>283000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>81000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,481 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4176000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3891000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4229000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4332000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4164000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3819000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4457000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3850000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3878000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3661000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3884000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3595000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3786000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3661000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4100000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3887000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3910000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3982000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4453000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3978000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3870000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4357000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3991000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4093000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4177000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4149000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4559000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2014000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2109000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2183000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2140000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2048000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2041000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1999000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2082000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2079000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1784000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1885000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1958000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1859000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1975000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1989000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1987000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2063000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2372000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2128000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2091000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2279000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2033000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>2258000</v>
       </c>
       <c r="AB9" s="3">
         <v>2258000</v>
       </c>
       <c r="AC9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="AD9" s="3">
         <v>2693000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2102000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1877000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2120000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2149000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2024000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1771000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2416000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1851000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1796000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1582000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2100000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1710000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1828000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1802000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2125000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1898000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1923000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1919000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2081000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1850000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1779000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2078000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1958000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1864000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1919000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1891000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1866000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,118 +1181,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>247000</v>
+        <v>244000</v>
       </c>
       <c r="E12" s="3">
         <v>247000</v>
       </c>
       <c r="F12" s="3">
+        <v>247000</v>
+      </c>
+      <c r="G12" s="3">
         <v>240000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>269000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>242000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>227000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>253000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>240000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>234000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>210000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>175000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>228000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>225000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>249000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>222000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>243000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>254000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>296000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>238000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>242000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>221000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>232000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>487000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>276000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>261000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>295000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>311000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>290000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>317000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>346000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>531000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>469000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>432000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>684000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1389,189 +1405,195 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E14" s="3">
         <v>188000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>922000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1053000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>823000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>877000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>495000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>416000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1324000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>512000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1978000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>321000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1683000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1502000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>893000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>183000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>247000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>360000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>374000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5077000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>516000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>764000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>561000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>832000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1323000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>561000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3804000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>855000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>520000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>205000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E15" s="3">
         <v>244000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>269000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>259000</v>
       </c>
       <c r="G15" s="3">
         <v>259000</v>
       </c>
       <c r="H15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="I15" s="3">
         <v>272000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>266000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>283000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>300000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>304000</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="N15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>23000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>24000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>25000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>27000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>31000</v>
       </c>
       <c r="V15" s="3">
         <v>31000</v>
       </c>
       <c r="W15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="X15" s="3">
         <v>30000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>35000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>34000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>35000</v>
       </c>
       <c r="AA15" s="3">
         <v>35000</v>
@@ -1580,28 +1602,28 @@
         <v>35000</v>
       </c>
       <c r="AC15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>24000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>51000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>41000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>46000</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
-      </c>
       <c r="AH15" s="3">
         <v>0</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>11</v>
+      <c r="AJ15" s="3">
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>11</v>
@@ -1609,8 +1631,11 @@
       <c r="AL15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1646,228 +1671,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3182000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3336000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3328000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3347000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3159000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3206000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3089000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3208000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3162000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4837000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3176000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4735000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4374000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4022000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3264000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3328000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3548000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4048000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8320000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3697000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4166000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3843000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4174000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4821000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4015000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7709000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E18" s="3">
         <v>709000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>893000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1004000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>817000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>660000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1251000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>761000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>670000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>499000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-953000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>419000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-949000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-713000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>78000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>623000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>582000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>434000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>405000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>173000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>191000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>148000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-81000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-644000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>134000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>378000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>895000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1906,284 +1938,291 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E20" s="3">
         <v>15000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>47000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>29000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>40000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>43000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-23000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-73000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-34000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-51000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-27000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>124000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>17000</v>
       </c>
       <c r="X20" s="3">
         <v>17000</v>
       </c>
       <c r="Y20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>22000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>20000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>30000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>290000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1114000</v>
+      </c>
+      <c r="E21" s="3">
         <v>938000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1177000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1216000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1070000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>903000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1529000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1004000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>927000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>805000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-656000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>717000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-577000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-410000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>325000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>943000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>853000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>759000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>773000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>572000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>607000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>586000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>340000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-174000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>586000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>501000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>460000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>865000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E22" s="3">
         <v>212000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>319000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>225000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>233000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>225000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>328000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>240000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>226000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>261000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>237000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>230000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>225000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>238000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>180000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>232000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>240000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>239000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>241000</v>
       </c>
       <c r="V22" s="3">
         <v>241000</v>
@@ -2195,269 +2234,278 @@
         <v>241000</v>
       </c>
       <c r="Y22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>209000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>219000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>226000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>227000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>231000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>240000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>231000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>218000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>221000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>219000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>526000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AK22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AL22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM22" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E23" s="3">
         <v>294000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-247000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-321000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-245000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-471000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>508000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>65000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-923000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-272000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>166000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-971000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-175000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>382000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>308000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>144000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>137000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-51000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-39000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-292000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-850000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-84000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-213000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>119000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>688000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E24" s="3">
         <v>74000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>69000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>630000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-52000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-12000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-19000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>149000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>107000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-900000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-24000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>76000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>98000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>62000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-21000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-104000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-179000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-236000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>46000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>54000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>57000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2566,228 +2614,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E26" s="3">
         <v>220000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-275000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-390000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-875000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-419000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>467000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>77000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-907000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-253000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>59000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-260000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-973000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-151000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>306000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>210000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>82000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>158000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>53000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>80000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-303000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-671000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-93000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>613000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>634000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E27" s="3">
         <v>214000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-217000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-437000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-846000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-139000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>463000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>69000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-872000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-220000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>56000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-232000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-955000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-159000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>292000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>207000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>77000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>150000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>140000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>69000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>109000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-314000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-689000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-105000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>530000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>580000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2896,8 +2953,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2958,8 +3018,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>11</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>11</v>
@@ -2976,11 +3036,11 @@
       <c r="AB29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>11</v>
@@ -2988,11 +3048,11 @@
       <c r="AF29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>11</v>
@@ -3006,8 +3066,11 @@
       <c r="AL29" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3116,8 +3179,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3226,228 +3292,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-47000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-29000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-40000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-43000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>23000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>73000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>34000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>51000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>27000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-17000</v>
       </c>
       <c r="X32" s="3">
         <v>-17000</v>
       </c>
       <c r="Y32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>40000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>56000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>777000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E33" s="3">
         <v>214000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-217000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-437000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-846000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-139000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>463000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>69000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-872000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-220000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>56000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-232000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-955000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-159000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>292000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>207000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>77000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>150000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>140000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>69000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>109000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-689000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-105000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>530000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>580000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3556,233 +3631,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E35" s="3">
         <v>214000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-217000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-437000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-846000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-139000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>463000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>69000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-872000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-220000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>56000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-232000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-955000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-159000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>292000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>207000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>77000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>150000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>140000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>69000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>109000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-689000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-105000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>530000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>580000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3821,8 +3905,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3861,118 +3946,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2161000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1697000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3300000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3319000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2258000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2991000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3226000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2249000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2669000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2143000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2801000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2225000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2058000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2175000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2165000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2045000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2436000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1743000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2177000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1827000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2402000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1804000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1975000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1241000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2165000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1973000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1782000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>963000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>680000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>599000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>900000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>988000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4081,448 +4170,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3564000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3384000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3059000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3462000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3766000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3456000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3408000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3385000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3539000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3435000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3696000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3730000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4471000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4253000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4529000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4046000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4488000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4572000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4581000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4385000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4545000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5189000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5676000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5254000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5260000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5108000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5822000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3497000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3247000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3007000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3959000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3927000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3949000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4021000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4051000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4109000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4118000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3833000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3859000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4049000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4012000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3818000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4167000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4362000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4406000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4403000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4516000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4361000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4290000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4422000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4636000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4850000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4782000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4731000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2314000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2182000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2180000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>447000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>585000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>565000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>574000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>571000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>542000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>477000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1721000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1639000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1586000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2011000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2061000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1896000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1536000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1680000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1844000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1432000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1473000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1601000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1391000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1411000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1530000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1568000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12620000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11528000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12552000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12314000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11632000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12297000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12485000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11425000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12088000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11501000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12051000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11453000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12164000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12451000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12573000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12154000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12822000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12401000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13005000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12160000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12781000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12884000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13464000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13805000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13431000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13794000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4541,11 +4645,11 @@
       <c r="H47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3">
         <v>8000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>11</v>
@@ -4553,8 +4657,8 @@
       <c r="L47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4631,228 +4735,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5168000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4994000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4948000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6036000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5931000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5982000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6147000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6028000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6130000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6171000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6158000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5990000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6181000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6396000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6477000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6547000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6658000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6641000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6855000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6709000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6611000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6710000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6950000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7111000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7232000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7302000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6868000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20091000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19666000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19565000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20880000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21341000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22063000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22564000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22410000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22856000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23763000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23903000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>24826000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25537000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27102000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>27506000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>28011000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>28541000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>28747000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>29547000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>29536000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34556000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>34746000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>36078000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>36535000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>37348000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>38013000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>38922000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4961,8 +5074,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5071,118 +5187,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E52" s="3">
         <v>465000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>462000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>458000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>434000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>471000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>463000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>477000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>443000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>449000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1899000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1983000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1110000</v>
       </c>
       <c r="Q52" s="3">
         <v>1110000</v>
       </c>
       <c r="R52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="S52" s="3">
         <v>1139000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1174000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1215000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1233000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1332000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1043000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>990000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>978000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1058000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1039000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1099000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5291,118 +5413,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40131000</v>
+      </c>
+      <c r="E54" s="3">
         <v>38415000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39326000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41758000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>41338000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42773000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43479000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42088000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43095000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43456000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44011000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>44252000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45932000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47059000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47666000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47851000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49195000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49004000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>50640000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49737000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>54991000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>55330000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>57470000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57246000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59424000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>59854000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60683000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5441,8 +5569,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5481,668 +5610,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2498000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2290000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2203000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2371000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2366000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2439000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2602000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2280000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2508000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2381000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1887000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1635000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1901000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1750000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1686000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1514000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1551000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1692000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1756000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1716000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1606000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1710000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1718000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1688000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1806000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1763000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1853000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E58" s="3">
         <v>421000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1868000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2580000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2094000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3060000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1769000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1479000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1980000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1023000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2109000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2769000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1719000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2077000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1426000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2709000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3530000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2697000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3188000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2106000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1649000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1630000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2345000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3130000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2771000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2790000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1700000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2848000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2737000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3074000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2864000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2939000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2822000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2351000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2361000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2341000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2374000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7473000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7130000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7376000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7786000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7915000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7602000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7610000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7700000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8220000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8281000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8496000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8982000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9611000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9289000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9875000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9475000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10769000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11861000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11157000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12796000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13797000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13037000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13792000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12247000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11394000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11843000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10411000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11469000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11534000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10996000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11613000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11027000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11825000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12691000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12089000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13164000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12103000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11751000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12322000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13674000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14107000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14452000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14028000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14322000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17078000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16518000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16316000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16695000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16828000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16878000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18504000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18819000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19036000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20013000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19103000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18497000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20363000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20840000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21617000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21037000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21602000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>22288000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22731000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23515000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24616000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>24473000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>24562000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>23812000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25955000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25828000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>26691000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3918000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4010000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3948000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4344000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4357000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3991000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3923000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3820000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3974000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3871000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4841000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4702000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4745000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4346000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3778000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3538000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3591000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3652000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3684000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3527000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3800000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3947000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4171000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4402000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3766000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4177000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3876000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6251,8 +6399,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6361,8 +6512,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6471,118 +6625,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33297000</v>
+      </c>
+      <c r="E66" s="3">
         <v>32146000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33606000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35374000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34775000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35230000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35353000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34577000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35387000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34845000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36207000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35484000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36895000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37715000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37388000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37384000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38871000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>39004000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>40614000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>40144000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>41139000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>41799000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>43498000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>43455000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45301000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>45122000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>45976000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6621,8 +6781,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6731,8 +6892,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6841,8 +7005,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6925,19 +7092,19 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AH70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AI70" s="3">
         <v>3620000</v>
@@ -6951,8 +7118,11 @@
       <c r="AL70" s="3">
         <v>3620000</v>
       </c>
+      <c r="AM70" s="3">
+        <v>3620000</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7061,118 +7231,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14676000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14958000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15173000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14956000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-14519000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7281,8 +7457,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7391,8 +7570,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7501,118 +7683,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6827000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6262000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5373000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6065000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6359000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7278000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7506000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6929000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7052000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7860000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7804000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8768000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9037000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9344000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10278000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10467000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10324000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10000000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10026000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9593000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13852000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13531000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13972000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13791000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14123000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14732000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14707000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7721,233 +7909,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E81" s="3">
         <v>214000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-217000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-437000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-846000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-139000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>463000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>69000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-872000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-220000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>56000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-232000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-955000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-159000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>292000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>207000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>77000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>150000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>140000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>69000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>109000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-689000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-105000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>530000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>580000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7986,118 +8183,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E83" s="3">
         <v>120000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>121000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>138000</v>
       </c>
       <c r="G83" s="3">
         <v>138000</v>
       </c>
       <c r="H83" s="3">
+        <v>138000</v>
+      </c>
+      <c r="I83" s="3">
         <v>139000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>150000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>156000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>146000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>123000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>306000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>321000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>358000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>323000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>320000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>329000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>305000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>376000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>395000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>381000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>382000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>399000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>416000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>413000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>450000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>443000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>382000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>474000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>479000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>507000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>528000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>527000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>577000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>480000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>332000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8206,8 +8407,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8316,8 +8520,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8426,8 +8633,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8536,8 +8746,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8646,118 +8859,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-105000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>575000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>693000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>103000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-124000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1184000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>324000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-145000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>973000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>544000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>122000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>456000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>529000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>218000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-405000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>331000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>307000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>273000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>305000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>538000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>325000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-227000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>112000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>367000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>421000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>162000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>741000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>470000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8796,118 +9015,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-127000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-129000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-148000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-97000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-124000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-119000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-149000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-119000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-139000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-142000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-122000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-127000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-153000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-146000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-113000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-150000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-176000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-143000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-131000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-128000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-169000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9016,8 +9239,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9126,118 +9352,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E94" s="3">
         <v>201000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>202000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>268000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>178000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>144000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>301000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>184000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>302000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>181000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>168000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>147000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>180000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>161000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>246000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>288000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>481000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>508000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>141000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>157000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>313000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>252000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>430000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>224000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>429000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>272000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>74000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>347000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>406000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>744000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9276,8 +9508,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9308,8 +9541,8 @@
       <c r="L96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9366,28 +9599,31 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AK96" s="3">
         <v>-346000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9496,8 +9732,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9606,8 +9845,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9716,334 +9958,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1744000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-674000</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="G100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-966000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-576000</v>
       </c>
       <c r="J100" s="3">
         <v>-576000</v>
       </c>
       <c r="K100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="L100" s="3">
         <v>-55000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-706000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-711000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-440000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-338000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-501000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-493000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-125000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-700000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-241000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-189000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-104000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>68000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-33000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-77000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>146000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-84000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-123000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-62000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>146000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-84000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-123000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-48000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-31000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-44000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>18000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>15000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>25000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>18000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>7000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>28000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1603000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1061000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-734000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-235000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>977000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-420000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>494000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-658000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>576000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>167000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-159000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>52000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>153000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-391000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>693000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-434000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>350000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-575000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>598000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-171000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>734000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>192000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>191000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>443000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>455000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>283000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>81000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,505 +656,517 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4711000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4480000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4176000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3891000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4229000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4332000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4164000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3819000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4457000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3850000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3878000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3661000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3884000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3595000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3786000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3661000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4100000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3887000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3910000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3982000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4453000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3978000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3870000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4357000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3991000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4093000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4177000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4149000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4559000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2056000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2176000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2074000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2014000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2109000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2183000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2140000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2048000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2041000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1999000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2082000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2079000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1784000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1885000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1958000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1859000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1975000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1989000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1987000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2063000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2372000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2128000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2091000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2279000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2033000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>2258000</v>
       </c>
       <c r="AD9" s="3">
         <v>2258000</v>
       </c>
       <c r="AE9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="AF9" s="3">
         <v>2693000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2655000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2304000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2102000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1877000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2120000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2149000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2024000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1771000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2416000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1851000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1796000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1582000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2100000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1710000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1828000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1802000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2125000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1898000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1923000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1919000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2081000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1850000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1779000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2078000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1958000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1864000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1919000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1891000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1866000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1195,124 +1207,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E12" s="3">
         <v>256000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>244000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>247000</v>
       </c>
       <c r="G12" s="3">
         <v>247000</v>
       </c>
       <c r="H12" s="3">
+        <v>247000</v>
+      </c>
+      <c r="I12" s="3">
         <v>240000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>269000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>242000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>227000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>253000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>240000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>234000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>210000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>175000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>228000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>225000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>249000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>222000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>243000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>254000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>296000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>238000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>242000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>221000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>232000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>487000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>276000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>261000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>295000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>311000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>290000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>317000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>346000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>531000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>469000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>432000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>684000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1427,201 +1443,207 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>985000</v>
+      </c>
+      <c r="E14" s="3">
         <v>184000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>439000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>188000</v>
       </c>
-      <c r="G14" s="3">
-        <v>922000</v>
-      </c>
       <c r="H14" s="3">
-        <v>1053000</v>
+        <v>945000</v>
       </c>
       <c r="I14" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="J14" s="3">
         <v>823000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>877000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>495000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>416000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1324000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>512000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1978000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>321000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1683000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1502000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>893000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>183000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>247000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>360000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>374000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5077000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>516000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>764000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>561000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>832000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1323000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>561000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3804000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>855000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>520000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>205000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E15" s="3">
         <v>249000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>251000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>244000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>269000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>259000</v>
       </c>
       <c r="I15" s="3">
         <v>259000</v>
       </c>
       <c r="J15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="K15" s="3">
         <v>272000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>266000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>283000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>300000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>304000</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>23000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>24000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>25000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>27000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>31000</v>
       </c>
       <c r="X15" s="3">
         <v>31000</v>
       </c>
       <c r="Y15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>30000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>35000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>34000</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>35000</v>
       </c>
       <c r="AC15" s="3">
         <v>35000</v>
@@ -1630,28 +1652,28 @@
         <v>35000</v>
       </c>
       <c r="AE15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>24000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>51000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>41000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>46000</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>11</v>
+      <c r="AL15" s="3">
+        <v>0</v>
       </c>
       <c r="AM15" s="3" t="s">
         <v>11</v>
@@ -1659,8 +1681,11 @@
       <c r="AN15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AO15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1698,240 +1723,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3426000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3414000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3282000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3182000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3336000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3313000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3349000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3347000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3159000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>3206000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3089000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>3162000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>4837000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>3176000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>4735000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>4374000</v>
+      </c>
+      <c r="T17" s="3">
+        <v>4022000</v>
+      </c>
+      <c r="U17" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="V17" s="3">
         <v>3328000</v>
       </c>
-      <c r="I17" s="3">
-        <v>3347000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3159000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3206000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3089000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3208000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3162000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>4837000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3176000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>4735000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>4374000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>4022000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>3264000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>3328000</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3548000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4048000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8320000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3697000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4166000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3843000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4174000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4821000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4015000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7709000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1285000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1066000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>894000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>709000</v>
       </c>
-      <c r="G18" s="3">
-        <v>893000</v>
-      </c>
       <c r="H18" s="3">
-        <v>1004000</v>
+        <v>916000</v>
       </c>
       <c r="I18" s="3">
+        <v>983000</v>
+      </c>
+      <c r="J18" s="3">
         <v>817000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>660000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1251000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>761000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>670000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>499000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-953000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>419000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-949000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-713000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>78000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>623000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>582000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>434000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>405000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>173000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>191000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>148000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-81000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-644000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>134000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>378000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>895000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1972,302 +2004,309 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E20" s="3">
         <v>29000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>31000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>47000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>29000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>40000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>43000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-20000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-73000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-34000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-51000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-27000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>124000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>17000</v>
       </c>
       <c r="Z20" s="3">
         <v>17000</v>
       </c>
       <c r="AA20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>22000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>8000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>20000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>14000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>290000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1523000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1286000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1114000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>938000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1177000</v>
-      </c>
       <c r="H21" s="3">
-        <v>1216000</v>
+        <v>1200000</v>
       </c>
       <c r="I21" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1070000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>903000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1529000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1004000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>927000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>805000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-656000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>717000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-577000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-410000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>325000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>943000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>853000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>759000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>773000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>572000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>607000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>586000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>340000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-174000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>586000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>501000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>460000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>865000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E22" s="3">
         <v>205000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>220000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>212000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>319000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>225000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>233000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>225000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>328000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>240000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>226000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>261000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>237000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>230000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>225000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>238000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>180000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>232000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>240000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>239000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>241000</v>
       </c>
       <c r="X22" s="3">
         <v>241000</v>
@@ -2279,281 +2318,290 @@
         <v>241000</v>
       </c>
       <c r="AA22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>209000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>219000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>226000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>227000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>231000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>240000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>231000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>218000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>221000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>219000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>526000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AM22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AN22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AO22" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E23" s="3">
         <v>648000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>204000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>294000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-247000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-321000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-245000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-471000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>508000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>65000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-923000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-272000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>166000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-971000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-175000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>382000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>308000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>144000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>137000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-51000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-33000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-292000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-850000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-84000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-213000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>119000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>688000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-390000</v>
+      </c>
+      <c r="E24" s="3">
         <v>214000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-78000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>74000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>69000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>630000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-52000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-12000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-19000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>149000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>107000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-900000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-24000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>76000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>98000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>62000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-104000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-119000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-179000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-236000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>46000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>54000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>57000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2668,240 +2716,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E26" s="3">
         <v>434000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>282000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>220000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-275000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-390000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-875000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-419000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>467000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>77000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-907000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-253000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>59000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-260000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-973000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-151000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>306000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>210000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>82000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>158000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>53000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>80000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-303000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-671000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-93000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>613000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>634000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E27" s="3">
         <v>433000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>282000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>214000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-217000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-437000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-846000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-139000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>463000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>69000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-872000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-220000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>56000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-232000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-955000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-159000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>292000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>207000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>77000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>150000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>140000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>69000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>109000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-689000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-105000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>530000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>580000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3016,8 +3073,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3084,8 +3144,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>11</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>11</v>
@@ -3102,11 +3162,11 @@
       <c r="AD29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>11</v>
@@ -3114,11 +3174,11 @@
       <c r="AH29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>11</v>
@@ -3132,8 +3192,11 @@
       <c r="AN29" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3248,8 +3311,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3364,240 +3430,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-29000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-31000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-47000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-29000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-40000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-43000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>23000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>20000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>73000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>34000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>51000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>27000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-17000</v>
       </c>
       <c r="Z32" s="3">
         <v>-17000</v>
       </c>
       <c r="AA32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>40000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>56000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>777000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E33" s="3">
         <v>433000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>282000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>214000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-217000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-437000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-846000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-139000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>463000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>69000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-872000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-220000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>56000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-232000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-955000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-159000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>292000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>207000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>77000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>150000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>140000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>69000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>109000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-689000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-105000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>530000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>580000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3712,245 +3787,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E35" s="3">
         <v>433000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>282000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>214000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-217000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-437000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-846000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-139000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>463000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>69000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-872000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-220000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>56000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-232000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-955000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-159000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>292000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>207000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>77000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>150000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>140000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>69000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>109000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-689000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-105000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>530000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>580000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3991,8 +4075,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4033,124 +4118,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3556000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2203000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2161000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1697000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3300000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3319000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2258000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2991000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3226000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2249000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2669000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2143000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2801000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2225000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2058000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2175000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2165000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2045000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2436000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1743000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2177000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2402000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1804000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1975000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1241000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2165000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1973000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1782000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>963000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>680000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>599000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>900000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>988000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4265,472 +4354,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3709000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3810000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3564000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3384000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3059000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3462000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3766000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3456000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3408000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3385000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3539000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3435000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3696000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3730000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4471000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4253000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4529000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4046000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4488000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4572000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4581000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4385000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4545000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5189000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5676000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5254000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5260000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5108000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5822000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3179000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3323000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3497000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3247000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3007000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3959000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3927000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3949000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4021000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4051000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4109000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4118000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3833000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3859000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4049000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4012000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3818000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4167000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4362000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4406000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4403000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4516000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4361000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4290000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4422000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4636000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4850000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4782000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4731000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2380000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2285000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2314000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2182000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2180000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>447000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>585000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>565000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>574000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>571000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>542000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>477000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1721000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1639000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1586000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2011000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2061000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1896000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1536000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1680000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1844000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1432000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1473000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1601000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1391000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1411000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1530000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1568000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13946000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12736000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12620000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11528000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12552000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12314000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11632000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12297000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12485000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11425000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12088000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11501000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12051000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11453000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12164000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12451000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12573000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12154000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12822000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12401000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13005000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12160000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12781000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12884000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13464000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13805000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13431000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13794000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4755,11 +4859,11 @@
       <c r="J47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L47" s="3">
         <v>8000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>11</v>
@@ -4767,8 +4871,8 @@
       <c r="N47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4845,240 +4949,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4425000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5162000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5168000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4994000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4948000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6036000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5931000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5982000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6147000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6028000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6130000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6171000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6158000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5990000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6181000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6396000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6477000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6547000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6658000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6641000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6855000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6709000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6611000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6710000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6950000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7111000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7232000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7302000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6868000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19781000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19881000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20091000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19666000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19565000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20880000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21341000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22063000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22564000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22410000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22856000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23763000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23903000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>24826000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>25537000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>27102000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>27506000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>28011000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>28541000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>28747000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>29547000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>29536000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>34556000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34746000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>36078000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>36535000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>37348000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>38013000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>38922000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5193,8 +5306,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5309,124 +5425,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E52" s="3">
         <v>443000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>471000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>465000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>462000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>458000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>434000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>471000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>463000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>477000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>443000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>449000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1899000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1983000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1110000</v>
       </c>
       <c r="S52" s="3">
         <v>1110000</v>
       </c>
       <c r="T52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="U52" s="3">
         <v>1139000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1174000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1215000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1233000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1332000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1043000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>990000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>978000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1058000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1039000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1099000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5541,124 +5663,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40748000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39856000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40131000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38415000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39326000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>41758000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>41338000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42773000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43479000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42088000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43095000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43456000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44011000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44252000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>45932000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47059000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47666000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47851000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49195000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49004000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>50640000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>49737000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>54991000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>55330000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57470000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57246000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59424000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59854000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>60683000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5699,8 +5827,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5741,704 +5870,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2531000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2355000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2498000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2290000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2203000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2371000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2366000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2439000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2602000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2280000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2508000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2381000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1887000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1635000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1901000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1750000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1686000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1514000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1551000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1692000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1756000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1716000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1606000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1718000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1688000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1806000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1763000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1853000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1914000</v>
+      </c>
+      <c r="E58" s="3">
         <v>24000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>464000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>421000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1868000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2580000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2094000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3060000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1769000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1479000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1980000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1023000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2109000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2769000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1719000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2077000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1426000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2709000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3530000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2697000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3188000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2106000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1649000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1630000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2345000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3130000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2771000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2790000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1700000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2930000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2889000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2848000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2737000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3074000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2864000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2939000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2822000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2351000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2361000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2341000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2374000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7473000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7130000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7376000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7786000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7915000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7602000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7610000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7700000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8220000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8281000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8496000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8982000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9611000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9289000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9875000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9475000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10769000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13456000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11491000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11861000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11157000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12796000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13797000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13037000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13792000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12247000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11394000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11843000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10411000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11469000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11534000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10996000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11613000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11027000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11825000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12691000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12089000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13164000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12103000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11751000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12322000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13674000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14107000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14452000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14028000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14322000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15316000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17067000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17078000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16518000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16316000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16695000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16828000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16878000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18504000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18819000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19036000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20013000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19103000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18497000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20363000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20840000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21617000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21037000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>21602000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22288000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22731000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>23515000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>24616000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>24473000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>24562000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>23812000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25955000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25828000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>26691000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3716000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3645000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3918000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4010000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3948000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4344000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4357000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3991000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3923000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3820000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3974000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3871000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4841000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4702000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4745000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4346000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3778000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3538000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3591000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3652000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3684000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3527000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3800000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3947000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4171000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4402000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3766000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4177000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3876000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6553,8 +6701,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6669,8 +6820,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6785,124 +6939,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32834000</v>
+      </c>
+      <c r="E66" s="3">
         <v>32602000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33297000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32146000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33606000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35374000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34775000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35230000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35353000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34577000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35387000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34845000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36207000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35484000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36895000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37715000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37388000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37384000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>38871000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>39004000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>40614000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>40144000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>41139000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>41799000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>43498000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>43455000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>45301000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>45122000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>45976000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6943,8 +7103,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7059,8 +7220,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7175,8 +7339,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7265,19 +7432,19 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AJ70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AK70" s="3">
         <v>3620000</v>
@@ -7291,8 +7458,11 @@
       <c r="AN70" s="3">
         <v>3620000</v>
       </c>
+      <c r="AO70" s="3">
+        <v>3620000</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7407,124 +7577,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13762000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14243000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14676000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14958000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15173000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-14956000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14519000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7639,8 +7815,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7755,8 +7934,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7871,124 +8053,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7910000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7250000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6827000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6262000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5373000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6065000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6359000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7278000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7506000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6929000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7052000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7860000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7804000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8768000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9037000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9344000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10278000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10467000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10324000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10000000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10026000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9593000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13852000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13531000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13972000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13791000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14123000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14732000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14707000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8103,245 +8291,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E81" s="3">
         <v>433000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>282000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>214000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-217000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-437000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-846000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-139000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>463000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>69000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-872000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-220000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>56000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-232000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-955000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-159000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>292000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>207000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>77000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>150000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>140000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>69000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>109000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-689000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-105000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>530000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>580000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8382,124 +8579,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>113000</v>
+        <v>125000</v>
       </c>
       <c r="E83" s="3">
         <v>113000</v>
       </c>
       <c r="F83" s="3">
+        <v>113000</v>
+      </c>
+      <c r="G83" s="3">
         <v>120000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>121000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>138000</v>
       </c>
       <c r="I83" s="3">
         <v>138000</v>
       </c>
       <c r="J83" s="3">
+        <v>138000</v>
+      </c>
+      <c r="K83" s="3">
         <v>139000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>150000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>156000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>146000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>123000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>306000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>321000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>358000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>323000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>320000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>329000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>305000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>376000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>395000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>381000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>382000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>399000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>416000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>413000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>450000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>443000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>382000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>474000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>479000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>507000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>528000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>527000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>577000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>480000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>332000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8614,8 +8815,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8730,8 +8934,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8846,8 +9053,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8962,8 +9172,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9078,124 +9291,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1158000</v>
+      </c>
+      <c r="E89" s="3">
         <v>369000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>227000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-105000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>575000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>693000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>103000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-124000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1184000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>324000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-145000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>973000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>544000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>122000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-49000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>456000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>529000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>218000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-405000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>331000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>307000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>273000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>305000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>538000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>325000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-227000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>112000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>367000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>421000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>162000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>741000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>470000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9236,124 +9455,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-136000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-96000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-127000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-129000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-148000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-97000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-124000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-119000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-149000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-119000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-139000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-142000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-122000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-127000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-157000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-153000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-146000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-113000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-150000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-176000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-143000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-131000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-128000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-119000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-169000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9468,8 +9691,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9584,124 +9810,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E94" s="3">
         <v>135000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>236000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>201000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>202000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>268000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>178000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>144000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>301000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>184000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>302000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>181000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>168000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>147000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>180000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>161000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>246000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>288000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>481000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>508000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>141000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>157000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>313000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>252000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>430000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>224000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>429000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>272000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>74000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>347000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>406000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>744000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9742,8 +9974,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9780,8 +10013,8 @@
       <c r="N96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9838,28 +10071,31 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AM96" s="3">
         <v>-346000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9974,8 +10210,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10090,8 +10329,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10206,352 +10448,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-453000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1744000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-674000</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="I100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-966000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-576000</v>
       </c>
       <c r="L100" s="3">
         <v>-576000</v>
       </c>
       <c r="M100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="N100" s="3">
         <v>-55000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-706000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-711000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-440000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-338000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-501000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-493000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-125000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-700000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-241000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-189000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="E101" s="3">
         <v>100000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-49000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-104000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>68000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-33000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-77000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>146000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-84000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-123000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-62000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>146000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-123000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-62000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-48000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-31000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-44000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>18000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>25000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>11000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>7000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>28000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1353000</v>
+      </c>
+      <c r="E102" s="3">
         <v>42000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>464000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1603000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1061000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-734000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-235000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>977000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-420000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>494000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-658000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>576000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>167000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-159000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>52000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>153000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-391000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>693000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-434000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>350000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-575000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>598000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-171000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>734000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>192000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>191000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>14000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>443000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>455000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>283000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>81000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-5427000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TEVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>TEVA</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3982000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4711000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4480000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4176000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3891000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4229000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4332000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4164000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3819000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4457000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3850000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3878000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3661000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3884000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3595000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3786000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3661000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4100000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3887000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3910000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3982000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4453000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3978000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3870000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4357000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3991000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4093000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4177000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4149000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4559000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4529000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4701000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5065000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5398000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5617000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5720000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5650000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6492000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5563000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2011000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2056000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2176000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2074000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2014000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2109000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2183000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2140000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2048000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2041000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1999000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2082000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2079000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1784000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1885000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1958000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1859000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1975000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1989000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1987000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2063000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2372000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2128000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2091000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2279000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2033000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2229000</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>2258000</v>
       </c>
       <c r="AE9" s="3">
         <v>2258000</v>
       </c>
       <c r="AF9" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="AG9" s="3">
         <v>2693000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2552000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2668000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2750000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3127000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2967000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2865000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2811000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3102000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1971000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2655000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2304000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2102000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1877000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2120000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2149000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2024000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1771000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2416000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1851000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1796000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1582000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2100000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1710000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1828000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1802000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2125000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1898000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1923000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1919000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2081000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1850000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1779000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2078000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1958000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1864000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1919000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1891000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1866000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1977000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2033000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2315000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2271000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2650000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2855000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2839000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3390000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2801000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,127 +1220,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E12" s="3">
         <v>267000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>256000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>244000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>247000</v>
       </c>
       <c r="H12" s="3">
         <v>247000</v>
       </c>
       <c r="I12" s="3">
+        <v>247000</v>
+      </c>
+      <c r="J12" s="3">
         <v>240000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>269000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>242000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>227000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>253000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>240000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>234000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>210000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>175000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>228000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>225000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>249000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>222000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>243000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>254000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>296000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>238000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>242000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>221000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>232000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>487000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>276000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>261000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>295000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>311000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>290000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>317000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>346000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>531000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>469000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>432000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>684000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>663000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1446,207 +1462,213 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E14" s="3">
         <v>985000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>184000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>439000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>188000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>945000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1032000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>823000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>877000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>495000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>416000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1324000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>512000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1978000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>321000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1683000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1502000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>893000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>183000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>247000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>360000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>374000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5077000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>516000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>764000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>561000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>832000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1323000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>561000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3804000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1165000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>855000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-417000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>13850000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>520000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>6842000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>205000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>1508000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E15" s="3">
         <v>260000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>249000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>251000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>244000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>269000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>259000</v>
       </c>
       <c r="J15" s="3">
         <v>259000</v>
       </c>
       <c r="K15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="L15" s="3">
         <v>272000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>266000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>283000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>300000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>304000</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>20000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>21000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>23000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>24000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>25000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>27000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>31000</v>
       </c>
       <c r="Y15" s="3">
         <v>31000</v>
       </c>
       <c r="Z15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>30000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>35000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>34000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>35000</v>
       </c>
       <c r="AD15" s="3">
         <v>35000</v>
@@ -1655,28 +1677,28 @@
         <v>35000</v>
       </c>
       <c r="AF15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>24000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>51000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>41000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
-      </c>
       <c r="AK15" s="3">
         <v>0</v>
       </c>
       <c r="AL15" s="3">
         <v>0</v>
       </c>
-      <c r="AM15" s="3" t="s">
-        <v>11</v>
+      <c r="AM15" s="3">
+        <v>0</v>
       </c>
       <c r="AN15" s="3" t="s">
         <v>11</v>
@@ -1684,8 +1706,11 @@
       <c r="AO15" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AP15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1724,246 +1749,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3219000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3426000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3414000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3282000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3182000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3313000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3349000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3347000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3159000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3206000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3089000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3208000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3162000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4837000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3176000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4735000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4374000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4022000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3264000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3328000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3548000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4048000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8320000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3697000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4166000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3843000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4174000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4821000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4015000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7709000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4715000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3607000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>18415000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5239000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>11462000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4755000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6629000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4798000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>763000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1285000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1066000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>894000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>709000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>916000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>983000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>817000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>660000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1251000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>761000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>670000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>499000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-953000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>419000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-949000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-713000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>78000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>623000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>582000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>434000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>405000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4342000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>173000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>191000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>148000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-81000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-644000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>134000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>16000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1458000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-13017000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>378000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-5742000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>895000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-137000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2005,311 +2037,318 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E20" s="3">
         <v>22000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>29000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>31000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>47000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>29000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>40000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>43000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-23000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-20000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-73000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-34000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-51000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>124000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>17000</v>
       </c>
       <c r="AA20" s="3">
         <v>17000</v>
       </c>
       <c r="AB20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>22000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>20000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>9000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>11000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>30000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>290000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-56000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-777000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>977000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1523000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1286000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1114000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>938000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1200000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1195000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1070000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>903000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1529000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1004000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>927000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>805000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-656000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>717000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-577000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-410000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>325000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>943000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>853000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>759000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>773000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3837000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>572000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>607000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>586000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>340000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-174000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>586000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2774000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>501000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>460000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1979000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-12459000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>865000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-4875000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-582000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1192000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E22" s="3">
         <v>280000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>205000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>220000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>212000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>319000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>225000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>233000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>225000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>328000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>240000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>226000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>261000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>237000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>230000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>225000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>238000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>180000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>232000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>240000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>239000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>241000</v>
       </c>
       <c r="Y22" s="3">
         <v>241000</v>
@@ -2321,287 +2360,296 @@
         <v>241000</v>
       </c>
       <c r="AB22" s="3">
+        <v>241000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>209000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>219000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>226000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>227000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>231000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>240000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>231000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>221000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>219000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>526000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>151000</v>
-      </c>
-      <c r="AN22" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AO22" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AP22" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>436000</v>
+      </c>
+      <c r="E23" s="3">
         <v>90000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>648000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>204000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>294000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-247000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-321000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-245000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-471000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>508000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>65000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-923000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-272000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1199000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>166000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1160000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-971000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-175000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>382000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>308000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>144000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>137000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4459000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-33000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-292000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-850000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-84000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3387000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-213000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-250000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1254000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-13208000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>119000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-5978000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>688000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-914000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>615000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-390000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>214000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-78000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>74000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>69000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>630000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-52000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>41000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-12000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-19000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>149000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>107000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-900000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-24000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>76000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>98000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>62000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-104000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-59000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-119000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>11000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-179000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-236000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-410000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-494000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>54000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>57000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>207000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2719,246 +2767,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E26" s="3">
         <v>480000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>434000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>282000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>220000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-275000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-390000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-875000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-419000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>467000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>77000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-907000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-253000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1348000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>59000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-260000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-973000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-151000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>306000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>210000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>82000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>158000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4475000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>53000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>80000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-303000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-671000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-93000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-187000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-174000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1208000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-12798000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>613000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-5956000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>634000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-971000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>408000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E27" s="3">
         <v>480000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>433000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>282000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>214000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-217000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-437000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-846000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-139000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>463000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>69000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-872000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-220000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1314000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>56000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-232000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-955000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-159000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>292000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>207000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>77000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>150000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>140000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>69000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>109000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-689000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-105000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2843000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-283000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-241000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1055000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-12661000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>530000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>580000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3076,8 +3133,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3147,8 +3207,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>11</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>11</v>
@@ -3165,11 +3225,11 @@
       <c r="AE29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-97000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>11</v>
@@ -3177,11 +3237,11 @@
       <c r="AI29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK29" s="3">
         <v>1061000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>11</v>
@@ -3195,8 +3255,11 @@
       <c r="AO29" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3314,8 +3377,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3433,246 +3499,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-29000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-31000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-47000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-29000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-40000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-43000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>23000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>20000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>73000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>34000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>51000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>27000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-124000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-17000</v>
       </c>
       <c r="AA32" s="3">
         <v>-17000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>40000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-290000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>56000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>777000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E33" s="3">
         <v>480000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>433000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>282000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>214000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-217000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-437000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-846000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-139000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>463000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>69000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-872000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-220000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1314000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>56000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-232000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-955000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-159000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>292000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>207000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>77000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>150000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>140000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>69000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>109000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-689000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-105000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-283000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-241000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1055000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>530000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>580000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3790,251 +3865,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E35" s="3">
         <v>480000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>433000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>282000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>214000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-217000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-437000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-846000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-139000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>463000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>69000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-872000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-220000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1314000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>56000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-232000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-955000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-159000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>292000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>207000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>77000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>150000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>140000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>69000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>109000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-689000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-105000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-283000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-241000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1055000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>530000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>580000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4076,8 +4160,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4119,127 +4204,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3741000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3556000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2203000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2161000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1697000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3300000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3319000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2258000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2991000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3226000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2249000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2669000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2143000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2801000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2225000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2058000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2175000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2165000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2045000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2436000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1743000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2177000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1827000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2402000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1804000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1975000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1241000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2165000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1973000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1782000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1875000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1861000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1418000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>963000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>680000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>599000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>900000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>988000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1557000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4357,484 +4446,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3393000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3709000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3810000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3564000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3384000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3059000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3462000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3766000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3456000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3408000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3385000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3539000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3435000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3696000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3730000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4471000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4253000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4529000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4046000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4488000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4572000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4581000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4385000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4545000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5189000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5676000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5254000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5260000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5108000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5822000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5665000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6061000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6289000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7128000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7424000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7320000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>7264000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>7523000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8071000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3176000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3179000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3323000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3497000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3247000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3007000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3959000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3927000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3949000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4021000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4051000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4109000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4118000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3833000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3859000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4049000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4012000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3818000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4167000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4362000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4406000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4403000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4516000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4361000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4290000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4422000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4636000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4850000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4782000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4731000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4971000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5113000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4924000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5060000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5132000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4954000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>5349000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2330000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2380000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2285000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2314000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2182000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2180000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>447000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>585000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>565000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>574000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>571000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>542000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>477000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1721000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1639000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1586000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2011000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2061000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1896000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1536000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1680000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1844000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1432000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1473000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1601000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1391000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1411000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1530000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1568000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1475000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1818000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1867000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2367000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3062000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1544000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1672000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3763000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2409000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13710000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13946000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12736000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12620000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11528000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12552000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12314000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11632000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12297000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12485000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11425000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12088000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11501000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12051000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11453000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12164000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12451000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12573000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12154000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12822000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12401000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13005000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12160000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12781000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12884000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>13464000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12542000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13805000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13431000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13794000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13881000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14711000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14687000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>15382000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>16226000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>14595000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>14835000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>17228000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>17386000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4862,11 +4966,11 @@
       <c r="K47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M47" s="3">
         <v>8000</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>11</v>
@@ -4874,8 +4978,8 @@
       <c r="O47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4952,246 +5056,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4333000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4425000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5162000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5168000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4994000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4948000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6036000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5931000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5982000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6147000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6028000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6130000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6171000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6158000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5990000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6181000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6396000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6477000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6547000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6658000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6641000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6855000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6709000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6611000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6710000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6950000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7111000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7232000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7302000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6868000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7101000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7213000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7420000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7673000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8001000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8043000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8160000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8073000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8379000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19431000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19781000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19881000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20091000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19666000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19565000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20880000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>21341000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22063000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22564000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22410000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22856000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23763000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23903000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>24826000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>25537000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>27102000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>27506000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>28011000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>28541000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>28747000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>29547000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>29536000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34556000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34746000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>36078000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>36535000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>37348000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>38013000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>38922000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>42930000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>43860000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>45779000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>46054000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>60270000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>61699000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>66215000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>65896000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>69853000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5309,8 +5422,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5428,127 +5544,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E52" s="3">
         <v>405000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>443000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>471000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>465000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>462000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>458000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>434000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>471000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>463000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>477000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>443000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>449000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1899000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1983000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2050000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1110000</v>
       </c>
       <c r="T52" s="3">
         <v>1110000</v>
       </c>
       <c r="U52" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="V52" s="3">
         <v>1139000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1174000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1215000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1233000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1332000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1043000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>990000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>978000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1058000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1099000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1149000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1295000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1506000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1585000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2066000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1860000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5666,127 +5788,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40040000</v>
+      </c>
+      <c r="E54" s="3">
         <v>40748000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39856000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>40131000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38415000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39326000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>41758000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41338000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42773000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43479000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>42088000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43095000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>43456000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44011000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44252000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>45932000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47059000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47666000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47851000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49195000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>49004000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>50640000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49737000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>54991000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>55330000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57470000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57246000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59424000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>59854000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>60683000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>65061000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>67030000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>69181000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>70615000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>86082000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>86355000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>91276000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>93057000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>98747000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5828,8 +5956,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5871,722 +6000,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2596000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2531000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2355000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2498000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2290000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2203000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2371000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2366000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2439000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2602000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2280000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2508000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2381000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1887000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1635000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1901000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1750000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1686000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1514000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1551000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1692000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1756000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1716000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1606000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1718000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1688000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1806000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1763000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1853000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1626000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1779000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1929000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2069000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2370000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2278000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2378000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2157000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4953000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2612000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1914000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>464000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>421000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1868000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2580000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2094000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3060000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1769000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1479000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1980000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1023000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2109000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2769000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1719000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2077000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1426000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2709000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3530000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2697000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3188000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2106000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1649000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1630000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2345000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3130000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2771000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2790000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1700000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2673000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1302000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3646000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2731000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1246000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1942000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3276000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3676000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2811000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2930000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2889000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2848000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2737000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3074000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2864000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2939000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2822000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2351000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2361000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2341000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2374000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7473000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7130000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7376000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7786000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7915000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7602000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7610000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7700000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8220000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8281000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8496000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8982000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9611000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9289000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9875000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9475000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10769000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10531000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11164000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11525000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12206000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>11842000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11933000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13055000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>10657000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13532000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13456000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11491000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11861000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11157000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12796000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13797000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13037000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13792000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12247000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11394000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11843000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10411000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11469000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11534000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10996000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11613000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11027000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11825000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12691000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12089000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13164000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12103000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11751000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12322000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13674000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14107000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14452000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14028000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14322000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14830000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>14215000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>14756000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>17921000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16943000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>15457000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>15903000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>18488000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>19286000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14313000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15316000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17067000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17078000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16518000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16316000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16695000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16828000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16878000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18504000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18819000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19036000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20013000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19103000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18497000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20363000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20840000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21617000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>21037000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21602000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22288000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22731000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>23515000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>24616000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>24473000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>24562000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>23812000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25955000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25828000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>26691000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>26792000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28949000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>29434000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28827000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>31970500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33806000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>32691000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>32522000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>33179000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3690000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3716000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3645000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3918000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4010000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3948000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4344000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4357000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3991000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3923000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3820000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3974000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3871000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4841000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4702000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4745000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4346000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3778000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3538000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3591000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3652000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3684000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3527000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3800000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3947000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4171000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4402000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3766000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4177000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3876000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4498000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4889000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5122000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6873500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7484000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6937000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>7054000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9254000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6704,8 +6852,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6823,8 +6974,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6942,127 +7096,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31808000</v>
+      </c>
+      <c r="E66" s="3">
         <v>32834000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32602000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33297000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32146000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33606000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35374000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34775000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35230000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35353000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34577000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35387000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34845000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36207000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>35484000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36895000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37715000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37388000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37384000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38871000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>39004000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>40614000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>40144000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>41139000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>41799000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>43498000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>43455000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>45301000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>45122000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>45976000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>47331000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>49092000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>50560000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>53256000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>57411000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>58361000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>57253000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>59720000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>63618000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7104,8 +7264,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7223,8 +7384,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7342,8 +7506,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7435,19 +7602,19 @@
         <v>0</v>
       </c>
       <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
         <v>3825000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>3760000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>3696000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>3631000</v>
-      </c>
-      <c r="AK70" s="3">
-        <v>3620000</v>
       </c>
       <c r="AL70" s="3">
         <v>3620000</v>
@@ -7461,8 +7628,11 @@
       <c r="AO70" s="3">
         <v>3620000</v>
       </c>
+      <c r="AP70" s="3">
+        <v>3620000</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7580,127 +7750,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13394000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13762000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14243000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14676000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-14958000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15173000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14956000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14519000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13673000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13534000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13870000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-13950000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13086000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12975000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11660000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11716000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11484000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10529000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10370000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10662000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10869000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-10946000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11096000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6747000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6887000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6956000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-7066000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-6752000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-6063000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5958000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3072000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2864000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-2688000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-3803000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7873000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>7430000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13809000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13607000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>14991000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7818,8 +7994,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7937,8 +8116,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8056,127 +8238,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8228000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7910000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7250000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6827000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6262000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5373000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6065000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6359000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7278000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7506000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6929000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7052000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7860000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7804000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8768000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9037000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9344000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10278000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10467000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10324000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10000000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10026000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9593000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13852000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13531000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13972000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13791000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14123000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14732000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14707000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13905000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14178000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14925000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13728000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>25051000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>24374000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>30403000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>29717000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>31509000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8294,251 +8482,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E81" s="3">
         <v>480000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>433000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>282000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>214000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-217000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-437000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-846000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-139000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>463000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>69000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-872000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-220000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1314000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>56000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-232000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-955000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-159000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>292000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>207000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>77000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>150000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4349000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>140000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>69000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>109000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-314000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-689000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-105000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-283000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-241000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1055000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-11600000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>530000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-6035000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>580000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>348000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8580,127 +8777,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E83" s="3">
         <v>125000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>113000</v>
       </c>
       <c r="F83" s="3">
         <v>113000</v>
       </c>
       <c r="G83" s="3">
+        <v>113000</v>
+      </c>
+      <c r="H83" s="3">
         <v>120000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>121000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>138000</v>
       </c>
       <c r="J83" s="3">
         <v>138000</v>
       </c>
       <c r="K83" s="3">
+        <v>138000</v>
+      </c>
+      <c r="L83" s="3">
         <v>139000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>150000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>156000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>146000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>123000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>306000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>321000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>358000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>323000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>320000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>329000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>305000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>376000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>395000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>381000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>382000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>399000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>416000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>413000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>450000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>443000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>382000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>474000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>479000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>507000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>528000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>527000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>577000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>480000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>332000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>577000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8818,8 +9019,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8937,8 +9141,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9056,8 +9263,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9175,8 +9385,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9294,127 +9507,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1158000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>369000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>227000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-105000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>575000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>693000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>103000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-124000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1184000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>324000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-145000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>973000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>544000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>122000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-49000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>456000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>529000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>218000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-405000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>331000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>307000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>273000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>305000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>538000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>325000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-227000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>112000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>367000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>421000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>162000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1496000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1179000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1117000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>741000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>470000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1425000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1461000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9456,127 +9675,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-168000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-142000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-136000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-127000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-129000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-148000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-97000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-124000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-119000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-149000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-119000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-139000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-142000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-122000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-127000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-157000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-153000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-146000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-113000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-150000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-176000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-143000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-128000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-119000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-169000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-213000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-163000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-212000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-202000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-221000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9694,8 +9917,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9813,127 +10039,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E94" s="3">
         <v>165000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>135000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>236000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>201000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>202000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>268000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>178000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>144000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>301000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>184000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>302000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>181000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>168000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>147000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>180000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>161000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>246000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>288000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>481000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>508000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>141000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>157000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>313000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>252000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>430000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>224000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>429000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>272000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>74000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>347000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>406000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1039000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1912000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>744000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-392000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1182000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-797000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-32301000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9975,8 +10207,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10016,8 +10249,8 @@
       <c r="O96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10074,28 +10307,31 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-123000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-345000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-346000</v>
       </c>
       <c r="AN96" s="3">
         <v>-346000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-346000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-340000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10213,8 +10449,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10332,8 +10571,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10451,361 +10693,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E100" s="3">
         <v>40000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-453000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1744000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-674000</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-966000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-151000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-576000</v>
       </c>
       <c r="M100" s="3">
         <v>-576000</v>
       </c>
       <c r="N100" s="3">
+        <v>-576000</v>
+      </c>
+      <c r="O100" s="3">
         <v>-55000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-706000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-711000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-440000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-338000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-501000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1177000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-493000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-125000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-700000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-241000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-189000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-499000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-705000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2091000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-651000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1768000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-701000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>25372000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-121000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-49000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-104000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>68000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-33000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-77000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>146000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-84000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-123000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-62000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>146000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-84000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-123000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-62000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-48000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-31000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-44000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>18000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>15000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>25000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-49000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-69000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>18000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>7000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>28000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-496000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1353000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>42000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>464000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1603000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1061000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-734000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-235000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>977000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-420000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>494000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-658000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>576000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>167000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-159000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>52000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>153000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-391000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>693000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-434000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>350000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-575000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>598000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-171000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>734000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-924000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>192000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>191000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-93000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>443000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>455000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>283000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>81000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-301000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-88000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-569000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-5427000</v>
       </c>
     </row>
